--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/14. technology.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/14. technology.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997FDF45-9DD3-47F4-BAC1-F25915EEC888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39FBC90-2292-47A4-933F-88EA3463BA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="0" windowWidth="11496" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="technology" sheetId="2" r:id="rId1"/>
@@ -9507,7 +9507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}">
-  <dimension ref="A1:F985"/>
+  <dimension ref="A1:F746"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
@@ -24437,1924 +24437,6 @@
       <c r="F746" s="3">
         <v>108</v>
       </c>
-    </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A747" s="3"/>
-      <c r="B747" s="4"/>
-      <c r="C747" s="5"/>
-      <c r="D747" s="11"/>
-      <c r="E747" s="5"/>
-      <c r="F747" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A748" s="3"/>
-      <c r="B748" s="4"/>
-      <c r="C748" s="5"/>
-      <c r="D748" s="11"/>
-      <c r="E748" s="5"/>
-      <c r="F748" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A749" s="3"/>
-      <c r="B749" s="4"/>
-      <c r="C749" s="5"/>
-      <c r="D749" s="11"/>
-      <c r="E749" s="5"/>
-      <c r="F749" s="3">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A750" s="3"/>
-      <c r="B750" s="4"/>
-      <c r="C750" s="5"/>
-      <c r="D750" s="11"/>
-      <c r="E750" s="5"/>
-      <c r="F750" s="3"/>
-    </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A751" s="3"/>
-      <c r="B751" s="4"/>
-      <c r="C751" s="5"/>
-      <c r="D751" s="11"/>
-      <c r="E751" s="5"/>
-      <c r="F751" s="3"/>
-    </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A752" s="3"/>
-      <c r="B752" s="4"/>
-      <c r="C752" s="5"/>
-      <c r="D752" s="11"/>
-      <c r="E752" s="5"/>
-      <c r="F752" s="3"/>
-    </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A753" s="3"/>
-      <c r="B753" s="4"/>
-      <c r="C753" s="5"/>
-      <c r="D753" s="11"/>
-      <c r="E753" s="5"/>
-      <c r="F753" s="3"/>
-    </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A754" s="3"/>
-      <c r="B754" s="4"/>
-      <c r="C754" s="5"/>
-      <c r="D754" s="11"/>
-      <c r="E754" s="5"/>
-      <c r="F754" s="3"/>
-    </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A755" s="3"/>
-      <c r="B755" s="4"/>
-      <c r="C755" s="5"/>
-      <c r="D755" s="11"/>
-      <c r="E755" s="5"/>
-      <c r="F755" s="3"/>
-    </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A756" s="3"/>
-      <c r="B756" s="4"/>
-      <c r="C756" s="5"/>
-      <c r="D756" s="11"/>
-      <c r="E756" s="5"/>
-      <c r="F756" s="3"/>
-    </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A757" s="3"/>
-      <c r="B757" s="4"/>
-      <c r="C757" s="5"/>
-      <c r="D757" s="11"/>
-      <c r="E757" s="5"/>
-      <c r="F757" s="3"/>
-    </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A758" s="3"/>
-      <c r="B758" s="4"/>
-      <c r="C758" s="5"/>
-      <c r="D758" s="11"/>
-      <c r="E758" s="5"/>
-      <c r="F758" s="3"/>
-    </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A759" s="3"/>
-      <c r="B759" s="4"/>
-      <c r="C759" s="5"/>
-      <c r="D759" s="11"/>
-      <c r="E759" s="5"/>
-      <c r="F759" s="3"/>
-    </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A760" s="3"/>
-      <c r="B760" s="4"/>
-      <c r="C760" s="5"/>
-      <c r="D760" s="11"/>
-      <c r="E760" s="5"/>
-      <c r="F760" s="3"/>
-    </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A761" s="3"/>
-      <c r="B761" s="4"/>
-      <c r="C761" s="5"/>
-      <c r="D761" s="11"/>
-      <c r="E761" s="5"/>
-      <c r="F761" s="3"/>
-    </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A762" s="3"/>
-      <c r="B762" s="4"/>
-      <c r="C762" s="5"/>
-      <c r="D762" s="11"/>
-      <c r="E762" s="5"/>
-      <c r="F762" s="3"/>
-    </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A763" s="3"/>
-      <c r="B763" s="4"/>
-      <c r="C763" s="5"/>
-      <c r="D763" s="11"/>
-      <c r="E763" s="5"/>
-      <c r="F763" s="3"/>
-    </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A764" s="3"/>
-      <c r="B764" s="4"/>
-      <c r="C764" s="5"/>
-      <c r="D764" s="11"/>
-      <c r="E764" s="5"/>
-      <c r="F764" s="3"/>
-    </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A765" s="3"/>
-      <c r="B765" s="4"/>
-      <c r="C765" s="5"/>
-      <c r="D765" s="11"/>
-      <c r="E765" s="5"/>
-      <c r="F765" s="3"/>
-    </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A766" s="3"/>
-      <c r="B766" s="4"/>
-      <c r="C766" s="5"/>
-      <c r="D766" s="11"/>
-      <c r="E766" s="5"/>
-      <c r="F766" s="3"/>
-    </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A767" s="3"/>
-      <c r="B767" s="4"/>
-      <c r="C767" s="5"/>
-      <c r="D767" s="11"/>
-      <c r="E767" s="5"/>
-      <c r="F767" s="3"/>
-    </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A768" s="3"/>
-      <c r="B768" s="4"/>
-      <c r="C768" s="5"/>
-      <c r="D768" s="11"/>
-      <c r="E768" s="5"/>
-      <c r="F768" s="3"/>
-    </row>
-    <row r="769" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A769" s="3"/>
-      <c r="B769" s="4"/>
-      <c r="C769" s="5"/>
-      <c r="D769" s="11"/>
-      <c r="E769" s="5"/>
-      <c r="F769" s="3"/>
-    </row>
-    <row r="770" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A770" s="3"/>
-      <c r="B770" s="4"/>
-      <c r="C770" s="5"/>
-      <c r="D770" s="11"/>
-      <c r="E770" s="5"/>
-      <c r="F770" s="3"/>
-    </row>
-    <row r="771" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A771" s="3"/>
-      <c r="B771" s="4"/>
-      <c r="C771" s="5"/>
-      <c r="D771" s="11"/>
-      <c r="E771" s="5"/>
-      <c r="F771" s="3"/>
-    </row>
-    <row r="772" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A772" s="3"/>
-      <c r="B772" s="4"/>
-      <c r="C772" s="5"/>
-      <c r="D772" s="11"/>
-      <c r="E772" s="5"/>
-      <c r="F772" s="3"/>
-    </row>
-    <row r="773" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A773" s="3"/>
-      <c r="B773" s="4"/>
-      <c r="C773" s="5"/>
-      <c r="D773" s="11"/>
-      <c r="E773" s="5"/>
-      <c r="F773" s="3"/>
-    </row>
-    <row r="774" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A774" s="3"/>
-      <c r="B774" s="4"/>
-      <c r="C774" s="5"/>
-      <c r="D774" s="11"/>
-      <c r="E774" s="5"/>
-      <c r="F774" s="3"/>
-    </row>
-    <row r="775" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A775" s="3"/>
-      <c r="B775" s="4"/>
-      <c r="C775" s="5"/>
-      <c r="D775" s="11"/>
-      <c r="E775" s="5"/>
-      <c r="F775" s="3"/>
-    </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A776" s="3"/>
-      <c r="B776" s="4"/>
-      <c r="C776" s="5"/>
-      <c r="D776" s="11"/>
-      <c r="E776" s="5"/>
-      <c r="F776" s="3"/>
-    </row>
-    <row r="777" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A777" s="3"/>
-      <c r="B777" s="4"/>
-      <c r="C777" s="5"/>
-      <c r="D777" s="11"/>
-      <c r="E777" s="5"/>
-      <c r="F777" s="3"/>
-    </row>
-    <row r="778" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A778" s="3"/>
-      <c r="B778" s="4"/>
-      <c r="C778" s="5"/>
-      <c r="D778" s="11"/>
-      <c r="E778" s="5"/>
-      <c r="F778" s="3"/>
-    </row>
-    <row r="779" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A779" s="3"/>
-      <c r="B779" s="4"/>
-      <c r="C779" s="5"/>
-      <c r="D779" s="11"/>
-      <c r="E779" s="5"/>
-      <c r="F779" s="3"/>
-    </row>
-    <row r="780" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A780" s="3"/>
-      <c r="B780" s="4"/>
-      <c r="C780" s="5"/>
-      <c r="D780" s="11"/>
-      <c r="E780" s="5"/>
-      <c r="F780" s="3"/>
-    </row>
-    <row r="781" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A781" s="3"/>
-      <c r="B781" s="4"/>
-      <c r="C781" s="5"/>
-      <c r="D781" s="11"/>
-      <c r="E781" s="5"/>
-      <c r="F781" s="3"/>
-    </row>
-    <row r="782" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A782" s="3"/>
-      <c r="B782" s="4"/>
-      <c r="C782" s="5"/>
-      <c r="D782" s="11"/>
-      <c r="E782" s="5"/>
-      <c r="F782" s="3"/>
-    </row>
-    <row r="783" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A783" s="3"/>
-      <c r="B783" s="4"/>
-      <c r="C783" s="5"/>
-      <c r="D783" s="11"/>
-      <c r="E783" s="5"/>
-      <c r="F783" s="3"/>
-    </row>
-    <row r="784" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A784" s="3"/>
-      <c r="B784" s="4"/>
-      <c r="C784" s="5"/>
-      <c r="D784" s="11"/>
-      <c r="E784" s="5"/>
-      <c r="F784" s="3"/>
-    </row>
-    <row r="785" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A785" s="3"/>
-      <c r="B785" s="4"/>
-      <c r="C785" s="5"/>
-      <c r="D785" s="11"/>
-      <c r="E785" s="5"/>
-      <c r="F785" s="3"/>
-    </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A786" s="3"/>
-      <c r="B786" s="4"/>
-      <c r="C786" s="5"/>
-      <c r="D786" s="11"/>
-      <c r="E786" s="5"/>
-      <c r="F786" s="3"/>
-    </row>
-    <row r="787" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A787" s="3"/>
-      <c r="B787" s="4"/>
-      <c r="C787" s="5"/>
-      <c r="D787" s="11"/>
-      <c r="E787" s="5"/>
-      <c r="F787" s="3"/>
-    </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A788" s="3"/>
-      <c r="B788" s="4"/>
-      <c r="C788" s="5"/>
-      <c r="D788" s="11"/>
-      <c r="E788" s="5"/>
-      <c r="F788" s="3"/>
-    </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A789" s="3"/>
-      <c r="B789" s="4"/>
-      <c r="C789" s="5"/>
-      <c r="D789" s="11"/>
-      <c r="E789" s="5"/>
-      <c r="F789" s="3"/>
-    </row>
-    <row r="790" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A790" s="3"/>
-      <c r="B790" s="4"/>
-      <c r="C790" s="5"/>
-      <c r="D790" s="11"/>
-      <c r="E790" s="5"/>
-      <c r="F790" s="3"/>
-    </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A791" s="3"/>
-      <c r="B791" s="4"/>
-      <c r="C791" s="5"/>
-      <c r="D791" s="11"/>
-      <c r="E791" s="5"/>
-      <c r="F791" s="3"/>
-    </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A792" s="3"/>
-      <c r="B792" s="4"/>
-      <c r="C792" s="5"/>
-      <c r="D792" s="11"/>
-      <c r="E792" s="5"/>
-      <c r="F792" s="3"/>
-    </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A793" s="3"/>
-      <c r="B793" s="4"/>
-      <c r="C793" s="5"/>
-      <c r="D793" s="11"/>
-      <c r="E793" s="5"/>
-      <c r="F793" s="3"/>
-    </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A794" s="3"/>
-      <c r="B794" s="4"/>
-      <c r="C794" s="5"/>
-      <c r="D794" s="11"/>
-      <c r="E794" s="5"/>
-      <c r="F794" s="3"/>
-    </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A795" s="3"/>
-      <c r="B795" s="4"/>
-      <c r="C795" s="5"/>
-      <c r="D795" s="11"/>
-      <c r="E795" s="5"/>
-      <c r="F795" s="3"/>
-    </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A796" s="3"/>
-      <c r="B796" s="4"/>
-      <c r="C796" s="5"/>
-      <c r="D796" s="11"/>
-      <c r="E796" s="5"/>
-      <c r="F796" s="3"/>
-    </row>
-    <row r="797" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A797" s="3"/>
-      <c r="B797" s="4"/>
-      <c r="C797" s="5"/>
-      <c r="D797" s="11"/>
-      <c r="E797" s="5"/>
-      <c r="F797" s="3"/>
-    </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A798" s="3"/>
-      <c r="B798" s="4"/>
-      <c r="C798" s="5"/>
-      <c r="D798" s="11"/>
-      <c r="E798" s="5"/>
-      <c r="F798" s="3"/>
-    </row>
-    <row r="799" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A799" s="3"/>
-      <c r="B799" s="4"/>
-      <c r="C799" s="5"/>
-      <c r="D799" s="11"/>
-      <c r="E799" s="5"/>
-      <c r="F799" s="3"/>
-    </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A800" s="3"/>
-      <c r="B800" s="4"/>
-      <c r="C800" s="5"/>
-      <c r="D800" s="11"/>
-      <c r="E800" s="5"/>
-      <c r="F800" s="3"/>
-    </row>
-    <row r="801" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A801" s="3"/>
-      <c r="B801" s="4"/>
-      <c r="C801" s="5"/>
-      <c r="D801" s="11"/>
-      <c r="E801" s="5"/>
-      <c r="F801" s="3"/>
-    </row>
-    <row r="802" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A802" s="3"/>
-      <c r="B802" s="4"/>
-      <c r="C802" s="5"/>
-      <c r="D802" s="11"/>
-      <c r="E802" s="5"/>
-      <c r="F802" s="3"/>
-    </row>
-    <row r="803" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A803" s="3"/>
-      <c r="B803" s="4"/>
-      <c r="C803" s="5"/>
-      <c r="D803" s="11"/>
-      <c r="E803" s="5"/>
-      <c r="F803" s="3"/>
-    </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A804" s="3"/>
-      <c r="B804" s="4"/>
-      <c r="C804" s="5"/>
-      <c r="D804" s="11"/>
-      <c r="E804" s="5"/>
-      <c r="F804" s="3"/>
-    </row>
-    <row r="805" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A805" s="3"/>
-      <c r="B805" s="4"/>
-      <c r="C805" s="5"/>
-      <c r="D805" s="11"/>
-      <c r="E805" s="5"/>
-      <c r="F805" s="3"/>
-    </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A806" s="3"/>
-      <c r="B806" s="4"/>
-      <c r="C806" s="5"/>
-      <c r="D806" s="11"/>
-      <c r="E806" s="5"/>
-      <c r="F806" s="3"/>
-    </row>
-    <row r="807" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A807" s="3"/>
-      <c r="B807" s="4"/>
-      <c r="C807" s="5"/>
-      <c r="D807" s="11"/>
-      <c r="E807" s="5"/>
-      <c r="F807" s="3"/>
-    </row>
-    <row r="808" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A808" s="3"/>
-      <c r="B808" s="4"/>
-      <c r="C808" s="5"/>
-      <c r="D808" s="11"/>
-      <c r="E808" s="5"/>
-      <c r="F808" s="3"/>
-    </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A809" s="3"/>
-      <c r="B809" s="4"/>
-      <c r="C809" s="5"/>
-      <c r="D809" s="11"/>
-      <c r="E809" s="5"/>
-      <c r="F809" s="3"/>
-    </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A810" s="3"/>
-      <c r="B810" s="4"/>
-      <c r="C810" s="5"/>
-      <c r="D810" s="11"/>
-      <c r="E810" s="5"/>
-      <c r="F810" s="3"/>
-    </row>
-    <row r="811" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A811" s="3"/>
-      <c r="B811" s="4"/>
-      <c r="C811" s="5"/>
-      <c r="D811" s="11"/>
-      <c r="E811" s="5"/>
-      <c r="F811" s="3"/>
-    </row>
-    <row r="812" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A812" s="3"/>
-      <c r="B812" s="4"/>
-      <c r="C812" s="5"/>
-      <c r="D812" s="11"/>
-      <c r="E812" s="5"/>
-      <c r="F812" s="3"/>
-    </row>
-    <row r="813" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A813" s="3"/>
-      <c r="B813" s="4"/>
-      <c r="C813" s="5"/>
-      <c r="D813" s="11"/>
-      <c r="E813" s="5"/>
-      <c r="F813" s="3"/>
-    </row>
-    <row r="814" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A814" s="3"/>
-      <c r="B814" s="4"/>
-      <c r="C814" s="5"/>
-      <c r="D814" s="11"/>
-      <c r="E814" s="5"/>
-      <c r="F814" s="3"/>
-    </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A815" s="3"/>
-      <c r="B815" s="4"/>
-      <c r="C815" s="5"/>
-      <c r="D815" s="11"/>
-      <c r="E815" s="5"/>
-      <c r="F815" s="3"/>
-    </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A816" s="3"/>
-      <c r="B816" s="4"/>
-      <c r="C816" s="5"/>
-      <c r="D816" s="11"/>
-      <c r="E816" s="5"/>
-      <c r="F816" s="3"/>
-    </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A817" s="3"/>
-      <c r="B817" s="4"/>
-      <c r="C817" s="5"/>
-      <c r="D817" s="11"/>
-      <c r="E817" s="5"/>
-      <c r="F817" s="3"/>
-    </row>
-    <row r="818" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A818" s="3"/>
-      <c r="B818" s="4"/>
-      <c r="C818" s="5"/>
-      <c r="D818" s="11"/>
-      <c r="E818" s="5"/>
-      <c r="F818" s="3"/>
-    </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A819" s="3"/>
-      <c r="B819" s="4"/>
-      <c r="C819" s="5"/>
-      <c r="D819" s="11"/>
-      <c r="E819" s="5"/>
-      <c r="F819" s="3"/>
-    </row>
-    <row r="820" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A820" s="3"/>
-      <c r="B820" s="4"/>
-      <c r="C820" s="5"/>
-      <c r="D820" s="11"/>
-      <c r="E820" s="5"/>
-      <c r="F820" s="3"/>
-    </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A821" s="3"/>
-      <c r="B821" s="4"/>
-      <c r="C821" s="5"/>
-      <c r="D821" s="11"/>
-      <c r="E821" s="5"/>
-      <c r="F821" s="3"/>
-    </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A822" s="3"/>
-      <c r="B822" s="4"/>
-      <c r="C822" s="5"/>
-      <c r="D822" s="11"/>
-      <c r="E822" s="5"/>
-      <c r="F822" s="3"/>
-    </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A823" s="3"/>
-      <c r="B823" s="4"/>
-      <c r="C823" s="5"/>
-      <c r="D823" s="11"/>
-      <c r="E823" s="5"/>
-      <c r="F823" s="3"/>
-    </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A824" s="3"/>
-      <c r="B824" s="4"/>
-      <c r="C824" s="5"/>
-      <c r="D824" s="11"/>
-      <c r="E824" s="5"/>
-      <c r="F824" s="3"/>
-    </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A825" s="3"/>
-      <c r="B825" s="4"/>
-      <c r="C825" s="5"/>
-      <c r="D825" s="11"/>
-      <c r="E825" s="5"/>
-      <c r="F825" s="3"/>
-    </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A826" s="3"/>
-      <c r="B826" s="4"/>
-      <c r="C826" s="5"/>
-      <c r="D826" s="11"/>
-      <c r="E826" s="5"/>
-      <c r="F826" s="3"/>
-    </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A827" s="3"/>
-      <c r="B827" s="4"/>
-      <c r="C827" s="5"/>
-      <c r="D827" s="11"/>
-      <c r="E827" s="5"/>
-      <c r="F827" s="3"/>
-    </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A828" s="3"/>
-      <c r="B828" s="4"/>
-      <c r="C828" s="5"/>
-      <c r="D828" s="11"/>
-      <c r="E828" s="5"/>
-      <c r="F828" s="3"/>
-    </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A829" s="3"/>
-      <c r="B829" s="4"/>
-      <c r="C829" s="5"/>
-      <c r="D829" s="11"/>
-      <c r="E829" s="5"/>
-      <c r="F829" s="3"/>
-    </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A830" s="3"/>
-      <c r="B830" s="4"/>
-      <c r="C830" s="5"/>
-      <c r="D830" s="11"/>
-      <c r="E830" s="5"/>
-      <c r="F830" s="3"/>
-    </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A831" s="3"/>
-      <c r="B831" s="4"/>
-      <c r="C831" s="5"/>
-      <c r="D831" s="11"/>
-      <c r="E831" s="5"/>
-      <c r="F831" s="3"/>
-    </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A832" s="3"/>
-      <c r="B832" s="4"/>
-      <c r="C832" s="5"/>
-      <c r="D832" s="11"/>
-      <c r="E832" s="5"/>
-      <c r="F832" s="3"/>
-    </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A833" s="3"/>
-      <c r="B833" s="4"/>
-      <c r="C833" s="5"/>
-      <c r="D833" s="11"/>
-      <c r="E833" s="5"/>
-      <c r="F833" s="3"/>
-    </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A834" s="3"/>
-      <c r="B834" s="4"/>
-      <c r="C834" s="5"/>
-      <c r="D834" s="11"/>
-      <c r="E834" s="5"/>
-      <c r="F834" s="3"/>
-    </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A835" s="3"/>
-      <c r="B835" s="4"/>
-      <c r="C835" s="5"/>
-      <c r="D835" s="11"/>
-      <c r="E835" s="5"/>
-      <c r="F835" s="3"/>
-    </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A836" s="3"/>
-      <c r="B836" s="4"/>
-      <c r="C836" s="5"/>
-      <c r="D836" s="11"/>
-      <c r="E836" s="5"/>
-      <c r="F836" s="3"/>
-    </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A837" s="3"/>
-      <c r="B837" s="4"/>
-      <c r="C837" s="5"/>
-      <c r="D837" s="11"/>
-      <c r="E837" s="5"/>
-      <c r="F837" s="3"/>
-    </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A838" s="3"/>
-      <c r="B838" s="4"/>
-      <c r="C838" s="5"/>
-      <c r="D838" s="11"/>
-      <c r="E838" s="5"/>
-      <c r="F838" s="3"/>
-    </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A839" s="3"/>
-      <c r="B839" s="4"/>
-      <c r="C839" s="5"/>
-      <c r="D839" s="11"/>
-      <c r="E839" s="5"/>
-      <c r="F839" s="3"/>
-    </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A840" s="3"/>
-      <c r="B840" s="4"/>
-      <c r="C840" s="5"/>
-      <c r="D840" s="11"/>
-      <c r="E840" s="5"/>
-      <c r="F840" s="3"/>
-    </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A841" s="3"/>
-      <c r="B841" s="4"/>
-      <c r="C841" s="5"/>
-      <c r="D841" s="11"/>
-      <c r="E841" s="5"/>
-      <c r="F841" s="3"/>
-    </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A842" s="3"/>
-      <c r="B842" s="4"/>
-      <c r="C842" s="5"/>
-      <c r="D842" s="11"/>
-      <c r="E842" s="5"/>
-      <c r="F842" s="3"/>
-    </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A843" s="3"/>
-      <c r="B843" s="4"/>
-      <c r="C843" s="5"/>
-      <c r="D843" s="11"/>
-      <c r="E843" s="5"/>
-      <c r="F843" s="3"/>
-    </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A844" s="3"/>
-      <c r="B844" s="4"/>
-      <c r="C844" s="5"/>
-      <c r="D844" s="11"/>
-      <c r="E844" s="5"/>
-      <c r="F844" s="3"/>
-    </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A845" s="3"/>
-      <c r="B845" s="4"/>
-      <c r="C845" s="5"/>
-      <c r="D845" s="11"/>
-      <c r="E845" s="5"/>
-      <c r="F845" s="3"/>
-    </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A846" s="3"/>
-      <c r="B846" s="4"/>
-      <c r="C846" s="5"/>
-      <c r="D846" s="11"/>
-      <c r="E846" s="5"/>
-      <c r="F846" s="3"/>
-    </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A847" s="3"/>
-      <c r="B847" s="4"/>
-      <c r="C847" s="5"/>
-      <c r="D847" s="11"/>
-      <c r="E847" s="5"/>
-      <c r="F847" s="3"/>
-    </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A848" s="3"/>
-      <c r="B848" s="4"/>
-      <c r="C848" s="5"/>
-      <c r="D848" s="11"/>
-      <c r="E848" s="5"/>
-      <c r="F848" s="3"/>
-    </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A849" s="3"/>
-      <c r="B849" s="4"/>
-      <c r="C849" s="5"/>
-      <c r="D849" s="11"/>
-      <c r="E849" s="5"/>
-      <c r="F849" s="3"/>
-    </row>
-    <row r="850" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A850" s="3"/>
-      <c r="B850" s="4"/>
-      <c r="C850" s="5"/>
-      <c r="D850" s="11"/>
-      <c r="E850" s="5"/>
-      <c r="F850" s="3"/>
-    </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A851" s="3"/>
-      <c r="B851" s="4"/>
-      <c r="C851" s="5"/>
-      <c r="D851" s="11"/>
-      <c r="E851" s="5"/>
-      <c r="F851" s="3"/>
-    </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A852" s="3"/>
-      <c r="B852" s="4"/>
-      <c r="C852" s="5"/>
-      <c r="D852" s="11"/>
-      <c r="E852" s="5"/>
-      <c r="F852" s="3"/>
-    </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A853" s="3"/>
-      <c r="B853" s="4"/>
-      <c r="C853" s="5"/>
-      <c r="D853" s="11"/>
-      <c r="E853" s="5"/>
-      <c r="F853" s="3"/>
-    </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A854" s="3"/>
-      <c r="B854" s="4"/>
-      <c r="C854" s="5"/>
-      <c r="D854" s="11"/>
-      <c r="E854" s="5"/>
-      <c r="F854" s="3"/>
-    </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A855" s="3"/>
-      <c r="B855" s="4"/>
-      <c r="C855" s="5"/>
-      <c r="D855" s="11"/>
-      <c r="E855" s="5"/>
-      <c r="F855" s="3"/>
-    </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A856" s="3"/>
-      <c r="B856" s="4"/>
-      <c r="C856" s="5"/>
-      <c r="D856" s="11"/>
-      <c r="E856" s="5"/>
-      <c r="F856" s="3"/>
-    </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A857" s="3"/>
-      <c r="B857" s="4"/>
-      <c r="C857" s="5"/>
-      <c r="D857" s="11"/>
-      <c r="E857" s="5"/>
-      <c r="F857" s="3"/>
-    </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A858" s="3"/>
-      <c r="B858" s="4"/>
-      <c r="C858" s="5"/>
-      <c r="D858" s="11"/>
-      <c r="E858" s="5"/>
-      <c r="F858" s="3"/>
-    </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A859" s="3"/>
-      <c r="B859" s="4"/>
-      <c r="C859" s="5"/>
-      <c r="D859" s="11"/>
-      <c r="E859" s="5"/>
-      <c r="F859" s="3"/>
-    </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A860" s="3"/>
-      <c r="B860" s="4"/>
-      <c r="C860" s="5"/>
-      <c r="D860" s="11"/>
-      <c r="E860" s="5"/>
-      <c r="F860" s="3"/>
-    </row>
-    <row r="861" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A861" s="3"/>
-      <c r="B861" s="4"/>
-      <c r="C861" s="5"/>
-      <c r="D861" s="11"/>
-      <c r="E861" s="5"/>
-      <c r="F861" s="3"/>
-    </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A862" s="3"/>
-      <c r="B862" s="4"/>
-      <c r="C862" s="5"/>
-      <c r="D862" s="11"/>
-      <c r="E862" s="5"/>
-      <c r="F862" s="3"/>
-    </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A863" s="3"/>
-      <c r="B863" s="4"/>
-      <c r="C863" s="5"/>
-      <c r="D863" s="11"/>
-      <c r="E863" s="5"/>
-      <c r="F863" s="3"/>
-    </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A864" s="3"/>
-      <c r="B864" s="4"/>
-      <c r="C864" s="5"/>
-      <c r="D864" s="11"/>
-      <c r="E864" s="5"/>
-      <c r="F864" s="3"/>
-    </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A865" s="3"/>
-      <c r="B865" s="4"/>
-      <c r="C865" s="5"/>
-      <c r="D865" s="11"/>
-      <c r="E865" s="5"/>
-      <c r="F865" s="3"/>
-    </row>
-    <row r="866" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A866" s="3"/>
-      <c r="B866" s="4"/>
-      <c r="C866" s="5"/>
-      <c r="D866" s="11"/>
-      <c r="E866" s="5"/>
-      <c r="F866" s="3"/>
-    </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A867" s="3"/>
-      <c r="B867" s="4"/>
-      <c r="C867" s="5"/>
-      <c r="D867" s="11"/>
-      <c r="E867" s="5"/>
-      <c r="F867" s="3"/>
-    </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A868" s="3"/>
-      <c r="B868" s="4"/>
-      <c r="C868" s="5"/>
-      <c r="D868" s="11"/>
-      <c r="E868" s="5"/>
-      <c r="F868" s="3"/>
-    </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A869" s="3"/>
-      <c r="B869" s="4"/>
-      <c r="C869" s="5"/>
-      <c r="D869" s="11"/>
-      <c r="E869" s="5"/>
-      <c r="F869" s="3"/>
-    </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A870" s="3"/>
-      <c r="B870" s="4"/>
-      <c r="C870" s="5"/>
-      <c r="D870" s="11"/>
-      <c r="E870" s="5"/>
-      <c r="F870" s="3"/>
-    </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A871" s="3"/>
-      <c r="B871" s="4"/>
-      <c r="C871" s="5"/>
-      <c r="D871" s="11"/>
-      <c r="E871" s="5"/>
-      <c r="F871" s="3"/>
-    </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A872" s="3"/>
-      <c r="B872" s="4"/>
-      <c r="C872" s="5"/>
-      <c r="D872" s="11"/>
-      <c r="E872" s="5"/>
-      <c r="F872" s="3"/>
-    </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A873" s="3"/>
-      <c r="B873" s="4"/>
-      <c r="C873" s="5"/>
-      <c r="D873" s="11"/>
-      <c r="E873" s="5"/>
-      <c r="F873" s="3"/>
-    </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A874" s="3"/>
-      <c r="B874" s="4"/>
-      <c r="C874" s="5"/>
-      <c r="D874" s="11"/>
-      <c r="E874" s="5"/>
-      <c r="F874" s="3"/>
-    </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A875" s="3"/>
-      <c r="B875" s="4"/>
-      <c r="C875" s="5"/>
-      <c r="D875" s="11"/>
-      <c r="E875" s="5"/>
-      <c r="F875" s="3"/>
-    </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A876" s="3"/>
-      <c r="B876" s="4"/>
-      <c r="C876" s="5"/>
-      <c r="D876" s="11"/>
-      <c r="E876" s="5"/>
-      <c r="F876" s="3"/>
-    </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A877" s="3"/>
-      <c r="B877" s="4"/>
-      <c r="C877" s="5"/>
-      <c r="D877" s="11"/>
-      <c r="E877" s="5"/>
-      <c r="F877" s="3"/>
-    </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A878" s="3"/>
-      <c r="B878" s="4"/>
-      <c r="C878" s="5"/>
-      <c r="D878" s="11"/>
-      <c r="E878" s="5"/>
-      <c r="F878" s="3"/>
-    </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A879" s="3"/>
-      <c r="B879" s="4"/>
-      <c r="C879" s="5"/>
-      <c r="D879" s="11"/>
-      <c r="E879" s="5"/>
-      <c r="F879" s="3"/>
-    </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A880" s="3"/>
-      <c r="B880" s="4"/>
-      <c r="C880" s="5"/>
-      <c r="D880" s="11"/>
-      <c r="E880" s="5"/>
-      <c r="F880" s="3"/>
-    </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A881" s="3"/>
-      <c r="B881" s="4"/>
-      <c r="C881" s="5"/>
-      <c r="D881" s="11"/>
-      <c r="E881" s="5"/>
-      <c r="F881" s="3"/>
-    </row>
-    <row r="882" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A882" s="3"/>
-      <c r="B882" s="4"/>
-      <c r="C882" s="5"/>
-      <c r="D882" s="11"/>
-      <c r="E882" s="5"/>
-      <c r="F882" s="3"/>
-    </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A883" s="3"/>
-      <c r="B883" s="4"/>
-      <c r="C883" s="5"/>
-      <c r="D883" s="11"/>
-      <c r="E883" s="5"/>
-      <c r="F883" s="3"/>
-    </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A884" s="3"/>
-      <c r="B884" s="4"/>
-      <c r="C884" s="5"/>
-      <c r="D884" s="11"/>
-      <c r="E884" s="5"/>
-      <c r="F884" s="3"/>
-    </row>
-    <row r="885" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A885" s="3"/>
-      <c r="B885" s="4"/>
-      <c r="C885" s="5"/>
-      <c r="D885" s="11"/>
-      <c r="E885" s="5"/>
-      <c r="F885" s="3"/>
-    </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A886" s="3"/>
-      <c r="B886" s="4"/>
-      <c r="C886" s="5"/>
-      <c r="D886" s="11"/>
-      <c r="E886" s="5"/>
-      <c r="F886" s="3"/>
-    </row>
-    <row r="887" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A887" s="3"/>
-      <c r="B887" s="4"/>
-      <c r="C887" s="5"/>
-      <c r="D887" s="11"/>
-      <c r="E887" s="5"/>
-      <c r="F887" s="3"/>
-    </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A888" s="3"/>
-      <c r="B888" s="4"/>
-      <c r="C888" s="5"/>
-      <c r="D888" s="11"/>
-      <c r="E888" s="5"/>
-      <c r="F888" s="3"/>
-    </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A889" s="3"/>
-      <c r="B889" s="4"/>
-      <c r="C889" s="5"/>
-      <c r="D889" s="11"/>
-      <c r="E889" s="5"/>
-      <c r="F889" s="3"/>
-    </row>
-    <row r="890" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A890" s="3"/>
-      <c r="B890" s="4"/>
-      <c r="C890" s="5"/>
-      <c r="D890" s="11"/>
-      <c r="E890" s="5"/>
-      <c r="F890" s="3"/>
-    </row>
-    <row r="891" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A891" s="3"/>
-      <c r="B891" s="4"/>
-      <c r="C891" s="5"/>
-      <c r="D891" s="11"/>
-      <c r="E891" s="5"/>
-      <c r="F891" s="3"/>
-    </row>
-    <row r="892" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A892" s="3"/>
-      <c r="B892" s="4"/>
-      <c r="C892" s="5"/>
-      <c r="D892" s="11"/>
-      <c r="E892" s="5"/>
-      <c r="F892" s="3"/>
-    </row>
-    <row r="893" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A893" s="3"/>
-      <c r="B893" s="4"/>
-      <c r="C893" s="5"/>
-      <c r="D893" s="11"/>
-      <c r="E893" s="5"/>
-      <c r="F893" s="3"/>
-    </row>
-    <row r="894" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A894" s="3"/>
-      <c r="B894" s="4"/>
-      <c r="C894" s="5"/>
-      <c r="D894" s="11"/>
-      <c r="E894" s="5"/>
-      <c r="F894" s="3"/>
-    </row>
-    <row r="895" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A895" s="3"/>
-      <c r="B895" s="4"/>
-      <c r="C895" s="5"/>
-      <c r="D895" s="11"/>
-      <c r="E895" s="5"/>
-      <c r="F895" s="3"/>
-    </row>
-    <row r="896" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A896" s="3"/>
-      <c r="B896" s="4"/>
-      <c r="C896" s="5"/>
-      <c r="D896" s="11"/>
-      <c r="E896" s="5"/>
-      <c r="F896" s="3"/>
-    </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A897" s="3"/>
-      <c r="B897" s="4"/>
-      <c r="C897" s="5"/>
-      <c r="D897" s="11"/>
-      <c r="E897" s="5"/>
-      <c r="F897" s="3"/>
-    </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A898" s="3"/>
-      <c r="B898" s="4"/>
-      <c r="C898" s="5"/>
-      <c r="D898" s="11"/>
-      <c r="E898" s="5"/>
-      <c r="F898" s="3"/>
-    </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A899" s="3"/>
-      <c r="B899" s="4"/>
-      <c r="C899" s="5"/>
-      <c r="D899" s="11"/>
-      <c r="E899" s="5"/>
-      <c r="F899" s="3"/>
-    </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A900" s="3"/>
-      <c r="B900" s="4"/>
-      <c r="C900" s="5"/>
-      <c r="D900" s="11"/>
-      <c r="E900" s="5"/>
-      <c r="F900" s="3"/>
-    </row>
-    <row r="901" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A901" s="3"/>
-      <c r="B901" s="4"/>
-      <c r="C901" s="5"/>
-      <c r="D901" s="11"/>
-      <c r="E901" s="5"/>
-      <c r="F901" s="3"/>
-    </row>
-    <row r="902" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A902" s="3"/>
-      <c r="B902" s="4"/>
-      <c r="C902" s="5"/>
-      <c r="D902" s="11"/>
-      <c r="E902" s="5"/>
-      <c r="F902" s="3"/>
-    </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A903" s="3"/>
-      <c r="B903" s="4"/>
-      <c r="C903" s="5"/>
-      <c r="D903" s="11"/>
-      <c r="E903" s="5"/>
-      <c r="F903" s="3"/>
-    </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A904" s="3"/>
-      <c r="B904" s="4"/>
-      <c r="C904" s="5"/>
-      <c r="D904" s="11"/>
-      <c r="E904" s="5"/>
-      <c r="F904" s="3"/>
-    </row>
-    <row r="905" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A905" s="3"/>
-      <c r="B905" s="4"/>
-      <c r="C905" s="5"/>
-      <c r="D905" s="11"/>
-      <c r="E905" s="5"/>
-      <c r="F905" s="3"/>
-    </row>
-    <row r="906" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A906" s="3"/>
-      <c r="B906" s="4"/>
-      <c r="C906" s="5"/>
-      <c r="D906" s="11"/>
-      <c r="E906" s="5"/>
-      <c r="F906" s="3"/>
-    </row>
-    <row r="907" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A907" s="3"/>
-      <c r="B907" s="4"/>
-      <c r="C907" s="5"/>
-      <c r="D907" s="11"/>
-      <c r="E907" s="5"/>
-      <c r="F907" s="3"/>
-    </row>
-    <row r="908" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A908" s="3"/>
-      <c r="B908" s="4"/>
-      <c r="C908" s="5"/>
-      <c r="D908" s="11"/>
-      <c r="E908" s="5"/>
-      <c r="F908" s="3"/>
-    </row>
-    <row r="909" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A909" s="3"/>
-      <c r="B909" s="4"/>
-      <c r="C909" s="5"/>
-      <c r="D909" s="11"/>
-      <c r="E909" s="5"/>
-      <c r="F909" s="3"/>
-    </row>
-    <row r="910" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A910" s="3"/>
-      <c r="B910" s="4"/>
-      <c r="C910" s="5"/>
-      <c r="D910" s="11"/>
-      <c r="E910" s="5"/>
-      <c r="F910" s="3"/>
-    </row>
-    <row r="911" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A911" s="3"/>
-      <c r="B911" s="4"/>
-      <c r="C911" s="5"/>
-      <c r="D911" s="11"/>
-      <c r="E911" s="5"/>
-      <c r="F911" s="3"/>
-    </row>
-    <row r="912" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A912" s="3"/>
-      <c r="B912" s="4"/>
-      <c r="C912" s="5"/>
-      <c r="D912" s="11"/>
-      <c r="E912" s="5"/>
-      <c r="F912" s="3"/>
-    </row>
-    <row r="913" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A913" s="3"/>
-      <c r="B913" s="4"/>
-      <c r="C913" s="5"/>
-      <c r="D913" s="11"/>
-      <c r="E913" s="5"/>
-      <c r="F913" s="3"/>
-    </row>
-    <row r="914" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A914" s="3"/>
-      <c r="B914" s="4"/>
-      <c r="C914" s="5"/>
-      <c r="D914" s="11"/>
-      <c r="E914" s="5"/>
-      <c r="F914" s="3"/>
-    </row>
-    <row r="915" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A915" s="3"/>
-      <c r="B915" s="4"/>
-      <c r="C915" s="5"/>
-      <c r="D915" s="11"/>
-      <c r="E915" s="5"/>
-      <c r="F915" s="3"/>
-    </row>
-    <row r="916" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A916" s="3"/>
-      <c r="B916" s="4"/>
-      <c r="C916" s="5"/>
-      <c r="D916" s="11"/>
-      <c r="E916" s="5"/>
-      <c r="F916" s="3"/>
-    </row>
-    <row r="917" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A917" s="3"/>
-      <c r="B917" s="4"/>
-      <c r="C917" s="5"/>
-      <c r="D917" s="11"/>
-      <c r="E917" s="5"/>
-      <c r="F917" s="3"/>
-    </row>
-    <row r="918" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A918" s="3"/>
-      <c r="B918" s="4"/>
-      <c r="C918" s="5"/>
-      <c r="D918" s="11"/>
-      <c r="E918" s="5"/>
-      <c r="F918" s="3"/>
-    </row>
-    <row r="919" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A919" s="3"/>
-      <c r="B919" s="4"/>
-      <c r="C919" s="5"/>
-      <c r="D919" s="11"/>
-      <c r="E919" s="5"/>
-      <c r="F919" s="3"/>
-    </row>
-    <row r="920" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A920" s="3"/>
-      <c r="B920" s="4"/>
-      <c r="C920" s="5"/>
-      <c r="D920" s="11"/>
-      <c r="E920" s="5"/>
-      <c r="F920" s="3"/>
-    </row>
-    <row r="921" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A921" s="3"/>
-      <c r="B921" s="4"/>
-      <c r="C921" s="5"/>
-      <c r="D921" s="11"/>
-      <c r="E921" s="5"/>
-      <c r="F921" s="3"/>
-    </row>
-    <row r="922" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A922" s="3"/>
-      <c r="B922" s="4"/>
-      <c r="C922" s="5"/>
-      <c r="D922" s="11"/>
-      <c r="E922" s="5"/>
-      <c r="F922" s="3"/>
-    </row>
-    <row r="923" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A923" s="3"/>
-      <c r="B923" s="4"/>
-      <c r="C923" s="5"/>
-      <c r="D923" s="11"/>
-      <c r="E923" s="5"/>
-      <c r="F923" s="3"/>
-    </row>
-    <row r="924" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A924" s="3"/>
-      <c r="B924" s="4"/>
-      <c r="C924" s="5"/>
-      <c r="D924" s="11"/>
-      <c r="E924" s="5"/>
-      <c r="F924" s="3"/>
-    </row>
-    <row r="925" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A925" s="3"/>
-      <c r="B925" s="4"/>
-      <c r="C925" s="5"/>
-      <c r="D925" s="11"/>
-      <c r="E925" s="5"/>
-      <c r="F925" s="3"/>
-    </row>
-    <row r="926" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A926" s="3"/>
-      <c r="B926" s="4"/>
-      <c r="C926" s="5"/>
-      <c r="D926" s="11"/>
-      <c r="E926" s="5"/>
-      <c r="F926" s="3"/>
-    </row>
-    <row r="927" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A927" s="3"/>
-      <c r="B927" s="4"/>
-      <c r="C927" s="5"/>
-      <c r="D927" s="11"/>
-      <c r="E927" s="5"/>
-      <c r="F927" s="3"/>
-    </row>
-    <row r="928" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A928" s="3"/>
-      <c r="B928" s="4"/>
-      <c r="C928" s="5"/>
-      <c r="D928" s="11"/>
-      <c r="E928" s="5"/>
-      <c r="F928" s="3"/>
-    </row>
-    <row r="929" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A929" s="3"/>
-      <c r="B929" s="4"/>
-      <c r="C929" s="5"/>
-      <c r="D929" s="11"/>
-      <c r="E929" s="5"/>
-      <c r="F929" s="3"/>
-    </row>
-    <row r="930" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A930" s="3"/>
-      <c r="B930" s="4"/>
-      <c r="C930" s="5"/>
-      <c r="D930" s="11"/>
-      <c r="E930" s="5"/>
-      <c r="F930" s="3"/>
-    </row>
-    <row r="931" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A931" s="3"/>
-      <c r="B931" s="4"/>
-      <c r="C931" s="5"/>
-      <c r="D931" s="11"/>
-      <c r="E931" s="5"/>
-      <c r="F931" s="3"/>
-    </row>
-    <row r="932" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A932" s="3"/>
-      <c r="B932" s="4"/>
-      <c r="C932" s="5"/>
-      <c r="D932" s="11"/>
-      <c r="E932" s="5"/>
-      <c r="F932" s="3"/>
-    </row>
-    <row r="933" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A933" s="3"/>
-      <c r="B933" s="4"/>
-      <c r="C933" s="5"/>
-      <c r="D933" s="11"/>
-      <c r="E933" s="5"/>
-      <c r="F933" s="3"/>
-    </row>
-    <row r="934" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A934" s="3"/>
-      <c r="B934" s="4"/>
-      <c r="C934" s="5"/>
-      <c r="D934" s="11"/>
-      <c r="E934" s="5"/>
-      <c r="F934" s="3"/>
-    </row>
-    <row r="935" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A935" s="3"/>
-      <c r="B935" s="4"/>
-      <c r="C935" s="5"/>
-      <c r="D935" s="11"/>
-      <c r="E935" s="5"/>
-      <c r="F935" s="3"/>
-    </row>
-    <row r="936" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A936" s="3"/>
-      <c r="B936" s="4"/>
-      <c r="C936" s="5"/>
-      <c r="D936" s="11"/>
-      <c r="E936" s="5"/>
-      <c r="F936" s="3"/>
-    </row>
-    <row r="937" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A937" s="3"/>
-      <c r="B937" s="4"/>
-      <c r="C937" s="5"/>
-      <c r="D937" s="11"/>
-      <c r="E937" s="5"/>
-      <c r="F937" s="3"/>
-    </row>
-    <row r="938" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A938" s="3"/>
-      <c r="B938" s="4"/>
-      <c r="C938" s="5"/>
-      <c r="D938" s="11"/>
-      <c r="E938" s="5"/>
-      <c r="F938" s="3"/>
-    </row>
-    <row r="939" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A939" s="3"/>
-      <c r="B939" s="4"/>
-      <c r="C939" s="5"/>
-      <c r="D939" s="11"/>
-      <c r="E939" s="5"/>
-      <c r="F939" s="3"/>
-    </row>
-    <row r="940" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A940" s="3"/>
-      <c r="B940" s="4"/>
-      <c r="C940" s="5"/>
-      <c r="D940" s="11"/>
-      <c r="E940" s="5"/>
-      <c r="F940" s="3"/>
-    </row>
-    <row r="941" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A941" s="3"/>
-      <c r="B941" s="4"/>
-      <c r="C941" s="5"/>
-      <c r="D941" s="11"/>
-      <c r="E941" s="5"/>
-      <c r="F941" s="3"/>
-    </row>
-    <row r="942" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A942" s="3"/>
-      <c r="B942" s="4"/>
-      <c r="C942" s="5"/>
-      <c r="D942" s="11"/>
-      <c r="E942" s="5"/>
-      <c r="F942" s="3"/>
-    </row>
-    <row r="943" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A943" s="3"/>
-      <c r="B943" s="4"/>
-      <c r="C943" s="5"/>
-      <c r="D943" s="11"/>
-      <c r="E943" s="5"/>
-      <c r="F943" s="3"/>
-    </row>
-    <row r="944" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A944" s="3"/>
-      <c r="B944" s="4"/>
-      <c r="C944" s="5"/>
-      <c r="D944" s="11"/>
-      <c r="E944" s="5"/>
-      <c r="F944" s="3"/>
-    </row>
-    <row r="945" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A945" s="3"/>
-      <c r="B945" s="4"/>
-      <c r="C945" s="5"/>
-      <c r="D945" s="11"/>
-      <c r="E945" s="5"/>
-      <c r="F945" s="3"/>
-    </row>
-    <row r="946" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A946" s="3"/>
-      <c r="B946" s="4"/>
-      <c r="C946" s="5"/>
-      <c r="D946" s="11"/>
-      <c r="E946" s="5"/>
-      <c r="F946" s="3"/>
-    </row>
-    <row r="947" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A947" s="3"/>
-      <c r="B947" s="4"/>
-      <c r="C947" s="5"/>
-      <c r="D947" s="11"/>
-      <c r="E947" s="5"/>
-      <c r="F947" s="3"/>
-    </row>
-    <row r="948" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A948" s="3"/>
-      <c r="B948" s="4"/>
-      <c r="C948" s="5"/>
-      <c r="D948" s="11"/>
-      <c r="E948" s="5"/>
-      <c r="F948" s="3"/>
-    </row>
-    <row r="949" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A949" s="3"/>
-      <c r="B949" s="4"/>
-      <c r="C949" s="5"/>
-      <c r="D949" s="11"/>
-      <c r="E949" s="5"/>
-      <c r="F949" s="3"/>
-    </row>
-    <row r="950" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A950" s="3"/>
-      <c r="B950" s="4"/>
-      <c r="C950" s="5"/>
-      <c r="D950" s="11"/>
-      <c r="E950" s="5"/>
-      <c r="F950" s="3"/>
-    </row>
-    <row r="951" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A951" s="3"/>
-      <c r="B951" s="4"/>
-      <c r="C951" s="5"/>
-      <c r="D951" s="11"/>
-      <c r="E951" s="5"/>
-      <c r="F951" s="3"/>
-    </row>
-    <row r="952" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A952" s="3"/>
-      <c r="B952" s="4"/>
-      <c r="C952" s="5"/>
-      <c r="D952" s="11"/>
-      <c r="E952" s="5"/>
-      <c r="F952" s="3"/>
-    </row>
-    <row r="953" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A953" s="3"/>
-      <c r="B953" s="4"/>
-      <c r="C953" s="5"/>
-      <c r="D953" s="11"/>
-      <c r="E953" s="5"/>
-      <c r="F953" s="3"/>
-    </row>
-    <row r="954" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A954" s="3"/>
-      <c r="B954" s="4"/>
-      <c r="C954" s="5"/>
-      <c r="D954" s="11"/>
-      <c r="E954" s="5"/>
-      <c r="F954" s="3"/>
-    </row>
-    <row r="955" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A955" s="3"/>
-      <c r="B955" s="4"/>
-      <c r="C955" s="5"/>
-      <c r="D955" s="11"/>
-      <c r="E955" s="5"/>
-      <c r="F955" s="3"/>
-    </row>
-    <row r="956" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A956" s="3"/>
-      <c r="B956" s="4"/>
-      <c r="C956" s="5"/>
-      <c r="D956" s="11"/>
-      <c r="E956" s="5"/>
-      <c r="F956" s="3"/>
-    </row>
-    <row r="957" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A957" s="3"/>
-      <c r="B957" s="4"/>
-      <c r="C957" s="5"/>
-      <c r="D957" s="11"/>
-      <c r="E957" s="5"/>
-      <c r="F957" s="3"/>
-    </row>
-    <row r="958" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A958" s="3"/>
-      <c r="B958" s="4"/>
-      <c r="C958" s="5"/>
-      <c r="D958" s="11"/>
-      <c r="E958" s="5"/>
-      <c r="F958" s="3"/>
-    </row>
-    <row r="959" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A959" s="3"/>
-      <c r="B959" s="4"/>
-      <c r="C959" s="5"/>
-      <c r="D959" s="11"/>
-      <c r="E959" s="5"/>
-      <c r="F959" s="3"/>
-    </row>
-    <row r="960" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A960" s="3"/>
-      <c r="B960" s="4"/>
-      <c r="C960" s="5"/>
-      <c r="D960" s="11"/>
-      <c r="E960" s="5"/>
-      <c r="F960" s="3"/>
-    </row>
-    <row r="961" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A961" s="3"/>
-      <c r="B961" s="4"/>
-      <c r="C961" s="5"/>
-      <c r="D961" s="11"/>
-      <c r="E961" s="5"/>
-      <c r="F961" s="3"/>
-    </row>
-    <row r="962" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A962" s="3"/>
-      <c r="B962" s="4"/>
-      <c r="C962" s="5"/>
-      <c r="D962" s="11"/>
-      <c r="E962" s="5"/>
-      <c r="F962" s="3"/>
-    </row>
-    <row r="963" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A963" s="3"/>
-      <c r="B963" s="4"/>
-      <c r="C963" s="5"/>
-      <c r="D963" s="11"/>
-      <c r="E963" s="5"/>
-      <c r="F963" s="3"/>
-    </row>
-    <row r="964" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A964" s="3"/>
-      <c r="B964" s="4"/>
-      <c r="C964" s="5"/>
-      <c r="D964" s="11"/>
-      <c r="E964" s="5"/>
-      <c r="F964" s="3"/>
-    </row>
-    <row r="965" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A965" s="3"/>
-      <c r="B965" s="4"/>
-      <c r="C965" s="5"/>
-      <c r="D965" s="11"/>
-      <c r="E965" s="5"/>
-      <c r="F965" s="3"/>
-    </row>
-    <row r="966" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A966" s="3"/>
-      <c r="B966" s="4"/>
-      <c r="C966" s="5"/>
-      <c r="D966" s="11"/>
-      <c r="E966" s="5"/>
-      <c r="F966" s="3"/>
-    </row>
-    <row r="967" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A967" s="3"/>
-      <c r="B967" s="4"/>
-      <c r="C967" s="5"/>
-      <c r="D967" s="11"/>
-      <c r="E967" s="5"/>
-      <c r="F967" s="3"/>
-    </row>
-    <row r="968" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A968" s="3"/>
-      <c r="B968" s="4"/>
-      <c r="C968" s="5"/>
-      <c r="D968" s="11"/>
-      <c r="E968" s="5"/>
-      <c r="F968" s="3"/>
-    </row>
-    <row r="969" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A969" s="3"/>
-      <c r="B969" s="4"/>
-      <c r="C969" s="5"/>
-      <c r="D969" s="11"/>
-      <c r="E969" s="5"/>
-      <c r="F969" s="3"/>
-    </row>
-    <row r="970" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A970" s="3"/>
-      <c r="B970" s="4"/>
-      <c r="C970" s="5"/>
-      <c r="D970" s="11"/>
-      <c r="E970" s="5"/>
-      <c r="F970" s="3"/>
-    </row>
-    <row r="971" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A971" s="3"/>
-      <c r="B971" s="4"/>
-      <c r="C971" s="5"/>
-      <c r="D971" s="11"/>
-      <c r="E971" s="5"/>
-      <c r="F971" s="3"/>
-    </row>
-    <row r="972" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A972" s="3"/>
-      <c r="B972" s="4"/>
-      <c r="C972" s="5"/>
-      <c r="D972" s="11"/>
-      <c r="E972" s="5"/>
-      <c r="F972" s="3"/>
-    </row>
-    <row r="973" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A973" s="3"/>
-      <c r="B973" s="4"/>
-      <c r="C973" s="5"/>
-      <c r="D973" s="11"/>
-      <c r="E973" s="5"/>
-      <c r="F973" s="3"/>
-    </row>
-    <row r="974" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A974" s="3"/>
-      <c r="B974" s="4"/>
-      <c r="C974" s="5"/>
-      <c r="D974" s="11"/>
-      <c r="E974" s="5"/>
-      <c r="F974" s="3"/>
-    </row>
-    <row r="975" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A975" s="3"/>
-      <c r="B975" s="4"/>
-      <c r="C975" s="5"/>
-      <c r="D975" s="11"/>
-      <c r="E975" s="5"/>
-      <c r="F975" s="3"/>
-    </row>
-    <row r="976" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A976" s="3"/>
-      <c r="B976" s="4"/>
-      <c r="C976" s="5"/>
-      <c r="D976" s="11"/>
-      <c r="E976" s="5"/>
-      <c r="F976" s="3"/>
-    </row>
-    <row r="977" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A977" s="3"/>
-      <c r="B977" s="4"/>
-      <c r="C977" s="5"/>
-      <c r="D977" s="11"/>
-      <c r="E977" s="5"/>
-      <c r="F977" s="3"/>
-    </row>
-    <row r="978" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A978" s="3"/>
-      <c r="B978" s="4"/>
-      <c r="C978" s="5"/>
-      <c r="D978" s="11"/>
-      <c r="E978" s="5"/>
-      <c r="F978" s="3"/>
-    </row>
-    <row r="979" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A979" s="3"/>
-      <c r="B979" s="4"/>
-      <c r="C979" s="5"/>
-      <c r="D979" s="11"/>
-      <c r="E979" s="5"/>
-      <c r="F979" s="3"/>
-    </row>
-    <row r="980" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A980" s="3"/>
-      <c r="B980" s="4"/>
-      <c r="C980" s="5"/>
-      <c r="D980" s="11"/>
-      <c r="E980" s="5"/>
-      <c r="F980" s="3"/>
-    </row>
-    <row r="981" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A981" s="3"/>
-      <c r="B981" s="4"/>
-      <c r="C981" s="5"/>
-      <c r="D981" s="11"/>
-      <c r="E981" s="5"/>
-      <c r="F981" s="3"/>
-    </row>
-    <row r="982" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A982" s="3"/>
-      <c r="B982" s="4"/>
-      <c r="C982" s="5"/>
-      <c r="D982" s="11"/>
-      <c r="E982" s="5"/>
-      <c r="F982" s="3"/>
-    </row>
-    <row r="983" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A983" s="3"/>
-      <c r="B983" s="4"/>
-      <c r="C983" s="5"/>
-      <c r="D983" s="11"/>
-      <c r="E983" s="5"/>
-      <c r="F983" s="3"/>
-    </row>
-    <row r="984" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A984" s="3"/>
-      <c r="B984" s="4"/>
-      <c r="C984" s="5"/>
-      <c r="D984" s="11"/>
-      <c r="E984" s="5"/>
-      <c r="F984" s="3"/>
-    </row>
-    <row r="985" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A985" s="3"/>
-      <c r="B985" s="4"/>
-      <c r="C985" s="5"/>
-      <c r="D985" s="11"/>
-      <c r="E985" s="5"/>
-      <c r="F985" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F742" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}"/>

--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/14. technology.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/14. technology.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\1. skill_area [13-17,5]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39FBC90-2292-47A4-933F-88EA3463BA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EFB0AC-FE42-4EC4-B4E7-18BD5400E374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-225" yWindow="210" windowWidth="13215" windowHeight="15165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="technology" sheetId="2" r:id="rId1"/>
@@ -9508,17 +9508,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}">
   <dimension ref="A1:F746"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.109375" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -9558,7 +9558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
@@ -9718,7 +9718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -9778,7 +9778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>34</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -9898,7 +9898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>102</v>
       </c>
@@ -9938,7 +9938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>129</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>103</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>104</v>
       </c>
@@ -9998,7 +9998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>105</v>
       </c>
@@ -10018,7 +10018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>106</v>
       </c>
@@ -10038,7 +10038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>107</v>
       </c>
@@ -10058,7 +10058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>108</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>109</v>
       </c>
@@ -10098,7 +10098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>110</v>
       </c>
@@ -10118,7 +10118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>111</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>112</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>113</v>
       </c>
@@ -10178,7 +10178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>114</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>115</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>116</v>
       </c>
@@ -10238,7 +10238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>117</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>118</v>
       </c>
@@ -10278,7 +10278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>119</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>120</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>121</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>122</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>123</v>
       </c>
@@ -10378,7 +10378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>124</v>
       </c>
@@ -10398,7 +10398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>125</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>126</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>127</v>
       </c>
@@ -10458,7 +10458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>128</v>
       </c>
@@ -10478,7 +10478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>235</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>236</v>
       </c>
@@ -10518,7 +10518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>237</v>
       </c>
@@ -10538,7 +10538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>238</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>239</v>
       </c>
@@ -10578,7 +10578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>240</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>241</v>
       </c>
@@ -10618,7 +10618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>242</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>243</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>244</v>
       </c>
@@ -10678,7 +10678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>284</v>
       </c>
@@ -10698,7 +10698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>285</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>286</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>287</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>288</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>289</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>290</v>
       </c>
@@ -10818,7 +10818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>291</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>321</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>322</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>323</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>324</v>
       </c>
@@ -10918,7 +10918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>337</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>325</v>
       </c>
@@ -10958,7 +10958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>326</v>
       </c>
@@ -10978,7 +10978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>327</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>328</v>
       </c>
@@ -11018,7 +11018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>363</v>
       </c>
@@ -11038,7 +11038,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>364</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>365</v>
       </c>
@@ -11078,7 +11078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>366</v>
       </c>
@@ -11098,7 +11098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>367</v>
       </c>
@@ -11118,7 +11118,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>368</v>
       </c>
@@ -11138,7 +11138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>369</v>
       </c>
@@ -11158,7 +11158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>370</v>
       </c>
@@ -11178,7 +11178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>371</v>
       </c>
@@ -11198,7 +11198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>372</v>
       </c>
@@ -11218,7 +11218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>412</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>378</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>379</v>
       </c>
@@ -11278,7 +11278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>413</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>414</v>
       </c>
@@ -11318,7 +11318,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>433</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>434</v>
       </c>
@@ -11358,7 +11358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>435</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>437</v>
       </c>
@@ -11398,7 +11398,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>438</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>440</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>465</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>470</v>
       </c>
@@ -11478,7 +11478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>474</v>
       </c>
@@ -11498,7 +11498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>477</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>480</v>
       </c>
@@ -11538,7 +11538,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>482</v>
       </c>
@@ -11558,7 +11558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>486</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>491</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>495</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>499</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>503</v>
       </c>
@@ -11658,7 +11658,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>504</v>
       </c>
@@ -11678,7 +11678,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>505</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>506</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>30</v>
       </c>
@@ -11738,7 +11738,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>523</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>522</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>530</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>543</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>548</v>
       </c>
@@ -11838,7 +11838,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>553</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>558</v>
       </c>
@@ -11878,7 +11878,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>563</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>568</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>572</v>
       </c>
@@ -11938,7 +11938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>577</v>
       </c>
@@ -11958,7 +11958,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="123" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>587</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="124" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>590</v>
       </c>
@@ -11998,7 +11998,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>595</v>
       </c>
@@ -12018,7 +12018,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="126" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>599</v>
       </c>
@@ -12038,7 +12038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="127" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>604</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>608</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>612</v>
       </c>
@@ -12098,7 +12098,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="130" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>617</v>
       </c>
@@ -12118,7 +12118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="131" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>622</v>
       </c>
@@ -12138,7 +12138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>627</v>
       </c>
@@ -12158,7 +12158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="133" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>631</v>
       </c>
@@ -12178,7 +12178,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>635</v>
       </c>
@@ -12198,7 +12198,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="135" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>640</v>
       </c>
@@ -12218,7 +12218,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="136" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>645</v>
       </c>
@@ -12238,7 +12238,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="137" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>650</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>654</v>
       </c>
@@ -12278,7 +12278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="139" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>659</v>
       </c>
@@ -12298,7 +12298,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>664</v>
       </c>
@@ -12318,7 +12318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>668</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>672</v>
       </c>
@@ -12358,7 +12358,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>676</v>
       </c>
@@ -12378,7 +12378,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>684</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>688</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>691</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>703</v>
       </c>
@@ -12458,7 +12458,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>708</v>
       </c>
@@ -12478,7 +12478,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="149" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>712</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>716</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>720</v>
       </c>
@@ -12538,7 +12538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="152" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>724</v>
       </c>
@@ -12558,7 +12558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="153" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>728</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>732</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>736</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>741</v>
       </c>
@@ -12638,7 +12638,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>746</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>751</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>755</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>759</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>763</v>
       </c>
@@ -12738,7 +12738,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>768</v>
       </c>
@@ -12758,7 +12758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>772</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>777</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>781</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="166" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" s="2" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>785</v>
       </c>
@@ -12838,7 +12838,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>789</v>
       </c>
@@ -12858,7 +12858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>793</v>
       </c>
@@ -12878,7 +12878,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>798</v>
       </c>
@@ -12898,7 +12898,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="170" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>801</v>
       </c>
@@ -12918,7 +12918,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="171" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>805</v>
       </c>
@@ -12938,7 +12938,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>809</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>813</v>
       </c>
@@ -12978,7 +12978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>816</v>
       </c>
@@ -12998,7 +12998,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>819</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>824</v>
       </c>
@@ -13038,7 +13038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>829</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>834</v>
       </c>
@@ -13078,7 +13078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>838</v>
       </c>
@@ -13098,7 +13098,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>843</v>
       </c>
@@ -13118,7 +13118,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="181" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>847</v>
       </c>
@@ -13138,7 +13138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="182" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>851</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="183" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>855</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="184" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>857</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="185" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>861</v>
       </c>
@@ -13218,7 +13218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>864</v>
       </c>
@@ -13238,7 +13238,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>439</v>
       </c>
@@ -13258,7 +13258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>440</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>873</v>
       </c>
@@ -13298,7 +13298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>876</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>880</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>884</v>
       </c>
@@ -13358,7 +13358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>887</v>
       </c>
@@ -13378,7 +13378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>891</v>
       </c>
@@ -13398,7 +13398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>895</v>
       </c>
@@ -13418,7 +13418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:6" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>899</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>902</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="198" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>906</v>
       </c>
@@ -13478,7 +13478,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="199" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
         <v>910</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="200" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>913</v>
       </c>
@@ -13518,7 +13518,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="201" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>917</v>
       </c>
@@ -13538,7 +13538,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="202" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>921</v>
       </c>
@@ -13558,7 +13558,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>926</v>
       </c>
@@ -13578,7 +13578,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="204" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>929</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="205" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
         <v>932</v>
       </c>
@@ -13618,7 +13618,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="206" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>936</v>
       </c>
@@ -13638,7 +13638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>941</v>
       </c>
@@ -13658,7 +13658,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>945</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>948</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>951</v>
       </c>
@@ -13718,7 +13718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>956</v>
       </c>
@@ -13738,7 +13738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="212" spans="1:6" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>959</v>
       </c>
@@ -13758,7 +13758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="213" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
         <v>962</v>
       </c>
@@ -13778,7 +13778,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="214" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>965</v>
       </c>
@@ -13798,7 +13798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="215" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>969</v>
       </c>
@@ -13818,7 +13818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>973</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>976</v>
       </c>
@@ -13858,7 +13858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>980</v>
       </c>
@@ -13878,7 +13878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="219" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>984</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="220" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>988</v>
       </c>
@@ -13918,7 +13918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="221" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>992</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>999</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
         <v>1003</v>
       </c>
@@ -13978,7 +13978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>1007</v>
       </c>
@@ -13998,7 +13998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="225" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>1012</v>
       </c>
@@ -14018,7 +14018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>1017</v>
       </c>
@@ -14038,7 +14038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>1021</v>
       </c>
@@ -14058,7 +14058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>1025</v>
       </c>
@@ -14078,7 +14078,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>1029</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:6" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>1033</v>
       </c>
@@ -14118,7 +14118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>1037</v>
       </c>
@@ -14138,7 +14138,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="232" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>1041</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>1044</v>
       </c>
@@ -14178,7 +14178,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>1047</v>
       </c>
@@ -14198,7 +14198,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>1049</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>1054</v>
       </c>
@@ -14238,7 +14238,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>1057</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="238" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>1061</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="239" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>1064</v>
       </c>
@@ -14298,7 +14298,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="240" spans="1:6" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>1067</v>
       </c>
@@ -14318,7 +14318,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
         <v>1071</v>
       </c>
@@ -14338,7 +14338,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>1075</v>
       </c>
@@ -14358,7 +14358,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>1079</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>1083</v>
       </c>
@@ -14398,7 +14398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>1086</v>
       </c>
@@ -14418,7 +14418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
         <v>1089</v>
       </c>
@@ -14438,7 +14438,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="247" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
         <v>1093</v>
       </c>
@@ -14458,7 +14458,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>1097</v>
       </c>
@@ -14478,7 +14478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
         <v>1101</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>436</v>
       </c>
@@ -14518,7 +14518,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="251" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>1108</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="252" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>1112</v>
       </c>
@@ -14558,7 +14558,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
         <v>1115</v>
       </c>
@@ -14578,7 +14578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="254" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>1120</v>
       </c>
@@ -14598,7 +14598,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="255" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
         <v>1124</v>
       </c>
@@ -14618,7 +14618,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="256" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>1128</v>
       </c>
@@ -14638,7 +14638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
         <v>1131</v>
       </c>
@@ -14658,7 +14658,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="258" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
         <v>1134</v>
       </c>
@@ -14678,7 +14678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
         <v>1137</v>
       </c>
@@ -14698,7 +14698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>1140</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="261" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
         <v>1144</v>
       </c>
@@ -14738,7 +14738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
         <v>1148</v>
       </c>
@@ -14758,7 +14758,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
         <v>1151</v>
       </c>
@@ -14778,7 +14778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>1157</v>
       </c>
@@ -14798,7 +14798,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
         <v>1162</v>
       </c>
@@ -14818,7 +14818,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>1165</v>
       </c>
@@ -14838,7 +14838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="267" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
         <v>1168</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
         <v>1171</v>
       </c>
@@ -14878,7 +14878,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="269" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
         <v>1174</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="270" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>1177</v>
       </c>
@@ -14918,7 +14918,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="271" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
         <v>1181</v>
       </c>
@@ -14938,7 +14938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>1184</v>
       </c>
@@ -14958,7 +14958,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="273" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
         <v>1187</v>
       </c>
@@ -14978,7 +14978,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="274" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>1190</v>
       </c>
@@ -14998,7 +14998,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="275" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>1193</v>
       </c>
@@ -15018,7 +15018,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="276" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>288</v>
       </c>
@@ -15038,7 +15038,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="277" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
         <v>1198</v>
       </c>
@@ -15058,7 +15058,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="278" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>1200</v>
       </c>
@@ -15078,7 +15078,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="279" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
         <v>1203</v>
       </c>
@@ -15098,7 +15098,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="280" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>768</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="281" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
         <v>755</v>
       </c>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="282" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>1209</v>
       </c>
@@ -15158,7 +15158,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
         <v>1212</v>
       </c>
@@ -15178,7 +15178,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>1215</v>
       </c>
@@ -15198,7 +15198,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="285" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>1155</v>
       </c>
@@ -15218,7 +15218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="286" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
         <v>1160</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
         <v>1220</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>1224</v>
       </c>
@@ -15278,7 +15278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>1229</v>
       </c>
@@ -15298,7 +15298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="290" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>1231</v>
       </c>
@@ -15318,7 +15318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="291" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
         <v>1233</v>
       </c>
@@ -15338,7 +15338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="292" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>1237</v>
       </c>
@@ -15358,7 +15358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
         <v>1242</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="294" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>1244</v>
       </c>
@@ -15398,7 +15398,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="295" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
         <v>1247</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="296" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>1251</v>
       </c>
@@ -15438,7 +15438,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="297" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
         <v>1255</v>
       </c>
@@ -15458,7 +15458,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="298" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>1257</v>
       </c>
@@ -15478,7 +15478,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="299" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
         <v>1260</v>
       </c>
@@ -15498,7 +15498,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="300" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>1264</v>
       </c>
@@ -15518,7 +15518,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="301" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
         <v>1269</v>
       </c>
@@ -15538,7 +15538,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="302" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>1272</v>
       </c>
@@ -15558,7 +15558,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="303" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
         <v>1275</v>
       </c>
@@ -15578,7 +15578,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="304" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>1280</v>
       </c>
@@ -15598,7 +15598,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="305" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
         <v>1283</v>
       </c>
@@ -15618,7 +15618,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>1286</v>
       </c>
@@ -15638,7 +15638,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="307" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
         <v>1289</v>
       </c>
@@ -15658,7 +15658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>1292</v>
       </c>
@@ -15678,7 +15678,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="309" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
         <v>1296</v>
       </c>
@@ -15698,7 +15698,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="310" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
         <v>1300</v>
       </c>
@@ -15718,7 +15718,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>1302</v>
       </c>
@@ -15738,7 +15738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="312" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
         <v>1306</v>
       </c>
@@ -15758,7 +15758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="313" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
         <v>1309</v>
       </c>
@@ -15778,7 +15778,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
         <v>1311</v>
       </c>
@@ -15798,7 +15798,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="315" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
         <v>1330</v>
       </c>
@@ -15818,7 +15818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="316" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
         <v>1335</v>
       </c>
@@ -15838,7 +15838,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="317" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
         <v>1339</v>
       </c>
@@ -15858,7 +15858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="318" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
         <v>1343</v>
       </c>
@@ -15878,7 +15878,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="319" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
         <v>1347</v>
       </c>
@@ -15898,7 +15898,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="320" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>1352</v>
       </c>
@@ -15918,7 +15918,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="321" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
         <v>1356</v>
       </c>
@@ -15938,7 +15938,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="322" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
         <v>1360</v>
       </c>
@@ -15958,7 +15958,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="323" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
         <v>1364</v>
       </c>
@@ -15978,7 +15978,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>1368</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
         <v>1371</v>
       </c>
@@ -16018,7 +16018,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="326" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>1375</v>
       </c>
@@ -16038,7 +16038,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
         <v>1378</v>
       </c>
@@ -16058,7 +16058,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A328" s="3" t="s">
         <v>1383</v>
       </c>
@@ -16078,7 +16078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="329" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>1387</v>
       </c>
@@ -16098,7 +16098,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="330" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>1391</v>
       </c>
@@ -16118,7 +16118,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="331" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A331" s="3" t="s">
         <v>1396</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="332" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
         <v>1400</v>
       </c>
@@ -16158,7 +16158,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="333" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
         <v>1403</v>
       </c>
@@ -16178,7 +16178,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="334" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
         <v>1406</v>
       </c>
@@ -16198,7 +16198,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="335" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
         <v>1410</v>
       </c>
@@ -16218,7 +16218,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="336" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
         <v>1412</v>
       </c>
@@ -16238,7 +16238,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="337" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
         <v>1416</v>
       </c>
@@ -16258,7 +16258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="338" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
         <v>1420</v>
       </c>
@@ -16278,7 +16278,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="339" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>1423</v>
       </c>
@@ -16298,7 +16298,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="340" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
         <v>1426</v>
       </c>
@@ -16318,7 +16318,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="341" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
         <v>1430</v>
       </c>
@@ -16338,7 +16338,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="342" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
         <v>1434</v>
       </c>
@@ -16358,7 +16358,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="343" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
         <v>1437</v>
       </c>
@@ -16378,7 +16378,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="344" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
         <v>1441</v>
       </c>
@@ -16398,7 +16398,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="345" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
         <v>996</v>
       </c>
@@ -16418,7 +16418,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="346" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
         <v>1447</v>
       </c>
@@ -16438,7 +16438,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="347" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
         <v>1450</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="348" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>1455</v>
       </c>
@@ -16478,7 +16478,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="349" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
         <v>1459</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="350" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
         <v>1462</v>
       </c>
@@ -16518,7 +16518,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="351" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
         <v>1466</v>
       </c>
@@ -16538,7 +16538,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="352" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
         <v>1471</v>
       </c>
@@ -16558,7 +16558,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="353" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
         <v>1476</v>
       </c>
@@ -16578,7 +16578,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="354" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>1480</v>
       </c>
@@ -16598,7 +16598,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="355" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
         <v>1484</v>
       </c>
@@ -16618,7 +16618,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="356" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>1488</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="357" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
         <v>1493</v>
       </c>
@@ -16658,7 +16658,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="358" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>1496</v>
       </c>
@@ -16678,7 +16678,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="359" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
         <v>1500</v>
       </c>
@@ -16698,7 +16698,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="360" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>1504</v>
       </c>
@@ -16718,7 +16718,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="361" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
         <v>1509</v>
       </c>
@@ -16738,7 +16738,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="362" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>1512</v>
       </c>
@@ -16758,7 +16758,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="363" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
         <v>1516</v>
       </c>
@@ -16778,7 +16778,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="364" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
         <v>1520</v>
       </c>
@@ -16798,7 +16798,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="365" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
         <v>1524</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="366" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>1527</v>
       </c>
@@ -16838,7 +16838,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="367" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
         <v>1530</v>
       </c>
@@ -16858,7 +16858,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="368" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>1533</v>
       </c>
@@ -16878,7 +16878,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="369" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
         <v>1537</v>
       </c>
@@ -16898,7 +16898,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="370" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
         <v>1540</v>
       </c>
@@ -16918,7 +16918,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
         <v>1544</v>
       </c>
@@ -16938,7 +16938,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="372" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
         <v>1547</v>
       </c>
@@ -16958,7 +16958,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="373" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
         <v>1551</v>
       </c>
@@ -16978,7 +16978,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>1554</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
         <v>1558</v>
       </c>
@@ -17018,7 +17018,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
         <v>1562</v>
       </c>
@@ -17038,7 +17038,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="377" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
         <v>1566</v>
       </c>
@@ -17058,7 +17058,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
         <v>1571</v>
       </c>
@@ -17078,7 +17078,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
         <v>1575</v>
       </c>
@@ -17098,7 +17098,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
         <v>1579</v>
       </c>
@@ -17118,7 +17118,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="381" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
         <v>1583</v>
       </c>
@@ -17138,7 +17138,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="382" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
         <v>1588</v>
       </c>
@@ -17158,7 +17158,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="383" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
         <v>1593</v>
       </c>
@@ -17178,7 +17178,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="384" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
         <v>1597</v>
       </c>
@@ -17198,7 +17198,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="385" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
         <v>1601</v>
       </c>
@@ -17218,7 +17218,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="386" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
         <v>1605</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="387" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
         <v>1610</v>
       </c>
@@ -17258,7 +17258,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="388" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
         <v>1615</v>
       </c>
@@ -17278,7 +17278,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="389" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
         <v>1618</v>
       </c>
@@ -17298,7 +17298,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="390" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
         <v>1623</v>
       </c>
@@ -17318,7 +17318,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="391" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
         <v>1626</v>
       </c>
@@ -17338,7 +17338,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
         <v>1629</v>
       </c>
@@ -17358,7 +17358,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="393" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
         <v>1412</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="394" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
         <v>1634</v>
       </c>
@@ -17398,7 +17398,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="395" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
         <v>1637</v>
       </c>
@@ -17418,7 +17418,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="396" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
         <v>1641</v>
       </c>
@@ -17438,7 +17438,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="397" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
         <v>1645</v>
       </c>
@@ -17458,7 +17458,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="398" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
         <v>1649</v>
       </c>
@@ -17478,7 +17478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="399" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
         <v>1653</v>
       </c>
@@ -17498,7 +17498,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="400" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
         <v>1657</v>
       </c>
@@ -17518,7 +17518,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="401" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
         <v>1661</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="402" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
         <v>1664</v>
       </c>
@@ -17558,7 +17558,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="403" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A403" s="3" t="s">
         <v>1668</v>
       </c>
@@ -17578,7 +17578,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="404" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
         <v>1671</v>
       </c>
@@ -17598,7 +17598,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="405" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
         <v>1675</v>
       </c>
@@ -17618,7 +17618,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="406" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
         <v>1678</v>
       </c>
@@ -17638,7 +17638,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="407" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
         <v>1679</v>
       </c>
@@ -17658,7 +17658,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="408" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
         <v>1680</v>
       </c>
@@ -17678,7 +17678,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="409" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A409" s="3" t="s">
         <v>1681</v>
       </c>
@@ -17698,7 +17698,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="410" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
         <v>1694</v>
       </c>
@@ -17718,7 +17718,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="411" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
         <v>1695</v>
       </c>
@@ -17738,7 +17738,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="412" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
         <v>1696</v>
       </c>
@@ -17758,7 +17758,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="413" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
         <v>1697</v>
       </c>
@@ -17778,7 +17778,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="414" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
         <v>1698</v>
       </c>
@@ -17798,7 +17798,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="415" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A415" s="3" t="s">
         <v>1699</v>
       </c>
@@ -17818,7 +17818,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="416" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
         <v>1717</v>
       </c>
@@ -17838,7 +17838,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="417" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
         <v>1718</v>
       </c>
@@ -17858,7 +17858,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="418" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A418" s="3" t="s">
         <v>1719</v>
       </c>
@@ -17878,7 +17878,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="419" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
         <v>1720</v>
       </c>
@@ -17898,7 +17898,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="420" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
         <v>1721</v>
       </c>
@@ -17918,7 +17918,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="421" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A421" s="3" t="s">
         <v>1722</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="422" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
         <v>1723</v>
       </c>
@@ -17958,7 +17958,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="423" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A423" s="3" t="s">
         <v>1745</v>
       </c>
@@ -17978,7 +17978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="424" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
         <v>1746</v>
       </c>
@@ -17998,7 +17998,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="425" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
         <v>1747</v>
       </c>
@@ -18018,7 +18018,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="426" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
         <v>1748</v>
       </c>
@@ -18038,7 +18038,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="427" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A427" s="3" t="s">
         <v>1749</v>
       </c>
@@ -18058,7 +18058,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="428" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
         <v>681</v>
       </c>
@@ -18078,7 +18078,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="429" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A429" s="3" t="s">
         <v>1765</v>
       </c>
@@ -18098,7 +18098,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="430" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A430" s="3" t="s">
         <v>1766</v>
       </c>
@@ -18118,7 +18118,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="431" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A431" s="3" t="s">
         <v>1767</v>
       </c>
@@ -18138,7 +18138,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="432" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A432" s="3" t="s">
         <v>1768</v>
       </c>
@@ -18158,7 +18158,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="433" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A433" s="3" t="s">
         <v>1782</v>
       </c>
@@ -18178,7 +18178,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="434" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
         <v>1786</v>
       </c>
@@ -18198,7 +18198,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="435" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
         <v>1790</v>
       </c>
@@ -18218,7 +18218,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="436" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
         <v>1791</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="437" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
         <v>1792</v>
       </c>
@@ -18258,7 +18258,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="438" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A438" s="3" t="s">
         <v>1803</v>
       </c>
@@ -18278,7 +18278,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="439" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A439" s="3" t="s">
         <v>1804</v>
       </c>
@@ -18298,7 +18298,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="440" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A440" s="3" t="s">
         <v>1805</v>
       </c>
@@ -18318,7 +18318,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="441" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A441" s="3" t="s">
         <v>1812</v>
       </c>
@@ -18338,7 +18338,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="442" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A442" s="3" t="s">
         <v>1813</v>
       </c>
@@ -18358,7 +18358,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="443" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
         <v>1814</v>
       </c>
@@ -18378,7 +18378,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="444" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
         <v>1815</v>
       </c>
@@ -18398,7 +18398,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="445" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A445" s="3" t="s">
         <v>1816</v>
       </c>
@@ -18418,7 +18418,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="446" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
         <v>1817</v>
       </c>
@@ -18438,7 +18438,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="447" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
         <v>1833</v>
       </c>
@@ -18458,7 +18458,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="448" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A448" s="3" t="s">
         <v>1834</v>
       </c>
@@ -18478,7 +18478,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="449" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
         <v>1835</v>
       </c>
@@ -18498,7 +18498,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="450" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A450" s="3" t="s">
         <v>1845</v>
       </c>
@@ -18518,7 +18518,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="451" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A451" s="3" t="s">
         <v>1846</v>
       </c>
@@ -18538,7 +18538,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="452" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A452" s="3" t="s">
         <v>1847</v>
       </c>
@@ -18558,7 +18558,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="453" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
         <v>1848</v>
       </c>
@@ -18578,7 +18578,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="454" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A454" s="3" t="s">
         <v>1849</v>
       </c>
@@ -18598,7 +18598,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="455" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A455" s="3" t="s">
         <v>1850</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="456" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
         <v>1851</v>
       </c>
@@ -18638,7 +18638,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="457" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A457" s="3" t="s">
         <v>1852</v>
       </c>
@@ -18658,7 +18658,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="458" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A458" s="3" t="s">
         <v>1878</v>
       </c>
@@ -18678,7 +18678,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="459" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A459" s="3" t="s">
         <v>1882</v>
       </c>
@@ -18698,7 +18698,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="460" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A460" s="3" t="s">
         <v>1886</v>
       </c>
@@ -18718,7 +18718,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="461" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A461" s="3" t="s">
         <v>1890</v>
       </c>
@@ -18738,7 +18738,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="462" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
         <v>1894</v>
       </c>
@@ -18758,7 +18758,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="463" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A463" s="3" t="s">
         <v>1898</v>
       </c>
@@ -18778,7 +18778,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="464" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
         <v>1902</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="465" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A465" s="3" t="s">
         <v>1906</v>
       </c>
@@ -18818,7 +18818,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="466" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A466" s="3" t="s">
         <v>1909</v>
       </c>
@@ -18838,7 +18838,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="467" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
         <v>538</v>
       </c>
@@ -18858,7 +18858,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="468" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A468" s="3" t="s">
         <v>539</v>
       </c>
@@ -18878,7 +18878,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="469" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A469" s="3" t="s">
         <v>541</v>
       </c>
@@ -18898,7 +18898,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="470" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
         <v>1921</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="471" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
         <v>1925</v>
       </c>
@@ -18938,7 +18938,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="472" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A472" s="3" t="s">
         <v>1928</v>
       </c>
@@ -18958,7 +18958,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="473" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
         <v>1933</v>
       </c>
@@ -18978,7 +18978,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="474" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
         <v>1936</v>
       </c>
@@ -18998,7 +18998,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="475" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A475" s="3" t="s">
         <v>557</v>
       </c>
@@ -19018,7 +19018,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="476" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
         <v>583</v>
       </c>
@@ -19038,7 +19038,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="477" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
         <v>582</v>
       </c>
@@ -19058,7 +19058,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="478" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A478" s="3" t="s">
         <v>585</v>
       </c>
@@ -19078,7 +19078,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
         <v>1949</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="480" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A480" s="3" t="s">
         <v>1953</v>
       </c>
@@ -19118,7 +19118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="481" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A481" s="3" t="s">
         <v>1957</v>
       </c>
@@ -19138,7 +19138,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="482" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
         <v>1961</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A483" s="3" t="s">
         <v>1965</v>
       </c>
@@ -19178,7 +19178,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="484" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A484" s="3" t="s">
         <v>1969</v>
       </c>
@@ -19198,7 +19198,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="485" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A485" s="3" t="s">
         <v>1973</v>
       </c>
@@ -19218,7 +19218,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="486" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
         <v>1977</v>
       </c>
@@ -19238,7 +19238,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="487" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A487" s="3" t="s">
         <v>1981</v>
       </c>
@@ -19258,7 +19258,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="488" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
         <v>700</v>
       </c>
@@ -19278,7 +19278,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="489" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A489" s="3" t="s">
         <v>1986</v>
       </c>
@@ -19298,7 +19298,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="490" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
         <v>1990</v>
       </c>
@@ -19318,7 +19318,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="491" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
         <v>1994</v>
       </c>
@@ -19338,7 +19338,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="492" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
         <v>1998</v>
       </c>
@@ -19358,7 +19358,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="493" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A493" s="3" t="s">
         <v>696</v>
       </c>
@@ -19378,7 +19378,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="494" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
         <v>2003</v>
       </c>
@@ -19398,7 +19398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="495" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
         <v>691</v>
       </c>
@@ -19418,7 +19418,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="496" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
         <v>2009</v>
       </c>
@@ -19438,7 +19438,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="497" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A497" s="3" t="s">
         <v>2013</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="498" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A498" s="3" t="s">
         <v>2017</v>
       </c>
@@ -19478,7 +19478,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="499" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A499" s="3" t="s">
         <v>2021</v>
       </c>
@@ -19498,7 +19498,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="500" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A500" s="3" t="s">
         <v>2025</v>
       </c>
@@ -19518,7 +19518,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="501" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A501" s="3" t="s">
         <v>2028</v>
       </c>
@@ -19538,7 +19538,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="502" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
         <v>2035</v>
       </c>
@@ -19558,7 +19558,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="503" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A503" s="3" t="s">
         <v>2038</v>
       </c>
@@ -19578,7 +19578,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="504" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
         <v>2041</v>
       </c>
@@ -19598,7 +19598,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="505" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A505" s="3" t="s">
         <v>2045</v>
       </c>
@@ -19618,7 +19618,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="506" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
         <v>2049</v>
       </c>
@@ -19638,7 +19638,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="507" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
         <v>2053</v>
       </c>
@@ -19658,7 +19658,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="508" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A508" s="3" t="s">
         <v>2057</v>
       </c>
@@ -19678,7 +19678,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="509" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A509" s="3" t="s">
         <v>2061</v>
       </c>
@@ -19698,7 +19698,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="510" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
         <v>2065</v>
       </c>
@@ -19718,7 +19718,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="511" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A511" s="3" t="s">
         <v>2069</v>
       </c>
@@ -19738,7 +19738,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="512" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
         <v>2073</v>
       </c>
@@ -19758,7 +19758,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="513" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A513" s="3" t="s">
         <v>2076</v>
       </c>
@@ -19778,7 +19778,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="514" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A514" s="3" t="s">
         <v>2079</v>
       </c>
@@ -19798,7 +19798,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="515" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A515" s="3" t="s">
         <v>2083</v>
       </c>
@@ -19818,7 +19818,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="516" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
         <v>2087</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="517" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A517" s="3" t="s">
         <v>2091</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="518" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
         <v>2095</v>
       </c>
@@ -19878,7 +19878,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="519" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A519" s="3" t="s">
         <v>2099</v>
       </c>
@@ -19898,7 +19898,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="520" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A520" s="3" t="s">
         <v>2103</v>
       </c>
@@ -19918,7 +19918,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="521" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A521" s="3" t="s">
         <v>2106</v>
       </c>
@@ -19938,7 +19938,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="522" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
         <v>2109</v>
       </c>
@@ -19958,7 +19958,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="523" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A523" s="3" t="s">
         <v>2113</v>
       </c>
@@ -19978,7 +19978,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="524" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A524" s="3" t="s">
         <v>2117</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="525" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A525" s="3" t="s">
         <v>2120</v>
       </c>
@@ -20018,7 +20018,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="526" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A526" s="3" t="s">
         <v>2124</v>
       </c>
@@ -20038,7 +20038,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="527" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A527" s="3" t="s">
         <v>2127</v>
       </c>
@@ -20058,7 +20058,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="528" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
         <v>2130</v>
       </c>
@@ -20078,7 +20078,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="529" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A529" s="3" t="s">
         <v>2134</v>
       </c>
@@ -20098,7 +20098,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="530" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
         <v>2137</v>
       </c>
@@ -20118,7 +20118,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="531" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A531" s="3" t="s">
         <v>2140</v>
       </c>
@@ -20138,7 +20138,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="532" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A532" s="3" t="s">
         <v>2143</v>
       </c>
@@ -20158,7 +20158,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="533" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A533" s="3" t="s">
         <v>2146</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="534" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A534" s="3" t="s">
         <v>2150</v>
       </c>
@@ -20198,7 +20198,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="535" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A535" s="3" t="s">
         <v>2153</v>
       </c>
@@ -20218,7 +20218,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="536" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
         <v>2157</v>
       </c>
@@ -20238,7 +20238,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="537" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A537" s="3" t="s">
         <v>2161</v>
       </c>
@@ -20258,7 +20258,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="538" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A538" s="3" t="s">
         <v>2164</v>
       </c>
@@ -20278,7 +20278,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="539" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A539" s="3" t="s">
         <v>2167</v>
       </c>
@@ -20298,7 +20298,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="540" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A540" s="3" t="s">
         <v>2171</v>
       </c>
@@ -20318,7 +20318,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="541" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A541" s="3" t="s">
         <v>2175</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="542" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A542" s="3" t="s">
         <v>2178</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="543" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A543" s="3" t="s">
         <v>2181</v>
       </c>
@@ -20378,7 +20378,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="544" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A544" s="3" t="s">
         <v>2184</v>
       </c>
@@ -20398,7 +20398,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="545" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A545" s="3" t="s">
         <v>2187</v>
       </c>
@@ -20418,7 +20418,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="546" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A546" s="3" t="s">
         <v>2190</v>
       </c>
@@ -20438,7 +20438,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="547" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A547" s="3" t="s">
         <v>2193</v>
       </c>
@@ -20458,7 +20458,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="548" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A548" s="3" t="s">
         <v>2196</v>
       </c>
@@ -20478,7 +20478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="549" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A549" s="3" t="s">
         <v>2199</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="550" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A550" s="3" t="s">
         <v>2203</v>
       </c>
@@ -20518,7 +20518,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="551" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A551" s="3" t="s">
         <v>2207</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="552" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A552" s="3" t="s">
         <v>2210</v>
       </c>
@@ -20558,7 +20558,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="553" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A553" s="3" t="s">
         <v>2213</v>
       </c>
@@ -20578,7 +20578,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="554" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A554" s="3" t="s">
         <v>2217</v>
       </c>
@@ -20598,7 +20598,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="555" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A555" s="3" t="s">
         <v>2221</v>
       </c>
@@ -20618,7 +20618,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="556" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A556" s="3" t="s">
         <v>2225</v>
       </c>
@@ -20638,7 +20638,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="557" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A557" s="3" t="s">
         <v>2229</v>
       </c>
@@ -20658,7 +20658,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="558" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A558" s="3" t="s">
         <v>2234</v>
       </c>
@@ -20678,7 +20678,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="559" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A559" s="3" t="s">
         <v>2238</v>
       </c>
@@ -20698,7 +20698,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="560" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A560" s="3" t="s">
         <v>2241</v>
       </c>
@@ -20718,7 +20718,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="561" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A561" s="3" t="s">
         <v>2246</v>
       </c>
@@ -20738,7 +20738,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="562" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A562" s="3" t="s">
         <v>2249</v>
       </c>
@@ -20758,7 +20758,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="563" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A563" s="3" t="s">
         <v>2252</v>
       </c>
@@ -20778,7 +20778,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="564" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A564" s="3" t="s">
         <v>2254</v>
       </c>
@@ -20798,7 +20798,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="565" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A565" s="3" t="s">
         <v>2258</v>
       </c>
@@ -20818,7 +20818,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="566" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A566" s="3" t="s">
         <v>2262</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="567" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A567" s="3" t="s">
         <v>2266</v>
       </c>
@@ -20858,7 +20858,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="568" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A568" s="3" t="s">
         <v>2270</v>
       </c>
@@ -20878,7 +20878,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="569" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A569" s="3" t="s">
         <v>2273</v>
       </c>
@@ -20898,7 +20898,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="570" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A570" s="3" t="s">
         <v>2277</v>
       </c>
@@ -20918,7 +20918,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="571" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A571" s="3" t="s">
         <v>2281</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="572" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A572" s="3" t="s">
         <v>2285</v>
       </c>
@@ -20958,7 +20958,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="573" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A573" s="3" t="s">
         <v>2288</v>
       </c>
@@ -20978,7 +20978,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="574" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A574" s="3" t="s">
         <v>2292</v>
       </c>
@@ -20998,7 +20998,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="575" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A575" s="3" t="s">
         <v>2296</v>
       </c>
@@ -21018,7 +21018,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="576" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A576" s="3" t="s">
         <v>2300</v>
       </c>
@@ -21038,7 +21038,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="577" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A577" s="3" t="s">
         <v>2304</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="578" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A578" s="3" t="s">
         <v>2308</v>
       </c>
@@ -21078,7 +21078,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="579" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A579" s="3" t="s">
         <v>2312</v>
       </c>
@@ -21098,7 +21098,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="580" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A580" s="3" t="s">
         <v>2316</v>
       </c>
@@ -21118,7 +21118,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="581" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A581" s="3" t="s">
         <v>2320</v>
       </c>
@@ -21138,7 +21138,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="582" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A582" s="3" t="s">
         <v>2324</v>
       </c>
@@ -21158,7 +21158,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="583" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A583" s="3" t="s">
         <v>2328</v>
       </c>
@@ -21178,7 +21178,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="584" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
         <v>2332</v>
       </c>
@@ -21198,7 +21198,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="585" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A585" s="3" t="s">
         <v>2338</v>
       </c>
@@ -21218,7 +21218,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="586" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A586" s="3" t="s">
         <v>2342</v>
       </c>
@@ -21238,7 +21238,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="587" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A587" s="3" t="s">
         <v>2346</v>
       </c>
@@ -21258,7 +21258,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="588" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A588" s="3" t="s">
         <v>2350</v>
       </c>
@@ -21278,7 +21278,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="589" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A589" s="3" t="s">
         <v>2354</v>
       </c>
@@ -21298,7 +21298,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="590" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A590" s="3" t="s">
         <v>2358</v>
       </c>
@@ -21318,7 +21318,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="591" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A591" s="3" t="s">
         <v>2362</v>
       </c>
@@ -21338,7 +21338,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="592" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A592" s="3" t="s">
         <v>2364</v>
       </c>
@@ -21358,7 +21358,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="593" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A593" s="3" t="s">
         <v>2367</v>
       </c>
@@ -21378,7 +21378,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="594" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A594" s="3" t="s">
         <v>2371</v>
       </c>
@@ -21398,7 +21398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="595" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A595" s="3" t="s">
         <v>2375</v>
       </c>
@@ -21418,7 +21418,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="596" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A596" s="3" t="s">
         <v>2377</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="597" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A597" s="3" t="s">
         <v>2381</v>
       </c>
@@ -21458,7 +21458,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="598" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A598" s="3" t="s">
         <v>2385</v>
       </c>
@@ -21478,7 +21478,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="599" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A599" s="3" t="s">
         <v>2389</v>
       </c>
@@ -21498,7 +21498,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="600" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A600" s="3" t="s">
         <v>2393</v>
       </c>
@@ -21518,7 +21518,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="601" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A601" s="3" t="s">
         <v>2397</v>
       </c>
@@ -21538,7 +21538,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="602" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A602" s="3" t="s">
         <v>2401</v>
       </c>
@@ -21558,7 +21558,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="603" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A603" s="3" t="s">
         <v>2404</v>
       </c>
@@ -21578,7 +21578,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="604" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A604" s="3" t="s">
         <v>2408</v>
       </c>
@@ -21598,7 +21598,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="605" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A605" s="3" t="s">
         <v>2412</v>
       </c>
@@ -21618,7 +21618,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="606" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A606" s="3" t="s">
         <v>2416</v>
       </c>
@@ -21638,7 +21638,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="607" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A607" s="3" t="s">
         <v>2421</v>
       </c>
@@ -21658,7 +21658,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="608" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A608" s="3" t="s">
         <v>2425</v>
       </c>
@@ -21678,7 +21678,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="609" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A609" s="3" t="s">
         <v>2429</v>
       </c>
@@ -21698,7 +21698,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="610" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A610" s="3" t="s">
         <v>2432</v>
       </c>
@@ -21718,7 +21718,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="611" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A611" s="3" t="s">
         <v>2436</v>
       </c>
@@ -21738,7 +21738,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="612" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A612" s="3" t="s">
         <v>2440</v>
       </c>
@@ -21758,7 +21758,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="613" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A613" s="3" t="s">
         <v>2443</v>
       </c>
@@ -21778,7 +21778,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="614" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A614" s="3" t="s">
         <v>2447</v>
       </c>
@@ -21798,7 +21798,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="615" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A615" s="3" t="s">
         <v>2032</v>
       </c>
@@ -21818,7 +21818,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="616" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A616" s="3" t="s">
         <v>2450</v>
       </c>
@@ -21838,7 +21838,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="617" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A617" s="3" t="s">
         <v>2454</v>
       </c>
@@ -21858,7 +21858,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="618" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A618" s="3" t="s">
         <v>2458</v>
       </c>
@@ -21878,7 +21878,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="619" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A619" s="3" t="s">
         <v>2462</v>
       </c>
@@ -21898,7 +21898,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="620" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A620" s="3" t="s">
         <v>2466</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="621" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A621" s="3" t="s">
         <v>2470</v>
       </c>
@@ -21938,7 +21938,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="622" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A622" s="3" t="s">
         <v>2474</v>
       </c>
@@ -21958,7 +21958,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="623" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A623" s="3" t="s">
         <v>2478</v>
       </c>
@@ -21978,7 +21978,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="624" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A624" s="3" t="s">
         <v>2482</v>
       </c>
@@ -21998,7 +21998,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="625" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A625" s="3" t="s">
         <v>2486</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="626" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A626" s="3" t="s">
         <v>2490</v>
       </c>
@@ -22038,7 +22038,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="627" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A627" s="3" t="s">
         <v>2494</v>
       </c>
@@ -22058,7 +22058,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="628" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A628" s="3" t="s">
         <v>2498</v>
       </c>
@@ -22078,7 +22078,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="629" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A629" s="3" t="s">
         <v>2502</v>
       </c>
@@ -22098,7 +22098,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="630" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A630" s="3" t="s">
         <v>2506</v>
       </c>
@@ -22118,7 +22118,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="631" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A631" s="3" t="s">
         <v>2510</v>
       </c>
@@ -22138,7 +22138,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="632" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A632" s="3" t="s">
         <v>2514</v>
       </c>
@@ -22158,7 +22158,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="633" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A633" s="3" t="s">
         <v>2518</v>
       </c>
@@ -22178,7 +22178,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="634" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A634" s="3" t="s">
         <v>2523</v>
       </c>
@@ -22198,7 +22198,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="635" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A635" s="3" t="s">
         <v>2527</v>
       </c>
@@ -22218,7 +22218,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="636" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A636" s="3" t="s">
         <v>2531</v>
       </c>
@@ -22238,7 +22238,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="637" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A637" s="3" t="s">
         <v>2535</v>
       </c>
@@ -22258,7 +22258,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="638" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A638" s="3" t="s">
         <v>2539</v>
       </c>
@@ -22278,7 +22278,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="639" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A639" s="3" t="s">
         <v>2543</v>
       </c>
@@ -22298,7 +22298,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="640" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A640" s="3" t="s">
         <v>2547</v>
       </c>
@@ -22318,7 +22318,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="641" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A641" s="3" t="s">
         <v>2551</v>
       </c>
@@ -22338,7 +22338,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="642" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A642" s="3" t="s">
         <v>2555</v>
       </c>
@@ -22358,7 +22358,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="643" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A643" s="3" t="s">
         <v>2559</v>
       </c>
@@ -22378,7 +22378,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="644" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A644" s="3" t="s">
         <v>2562</v>
       </c>
@@ -22398,7 +22398,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="645" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A645" s="3" t="s">
         <v>2565</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="646" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A646" s="3" t="s">
         <v>2568</v>
       </c>
@@ -22438,7 +22438,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="647" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A647" s="3" t="s">
         <v>2572</v>
       </c>
@@ -22458,7 +22458,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="648" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A648" s="3" t="s">
         <v>2576</v>
       </c>
@@ -22478,7 +22478,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="649" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A649" s="3" t="s">
         <v>2581</v>
       </c>
@@ -22498,7 +22498,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="650" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A650" s="3" t="s">
         <v>2585</v>
       </c>
@@ -22518,7 +22518,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="651" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A651" s="3" t="s">
         <v>2588</v>
       </c>
@@ -22538,7 +22538,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="652" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A652" s="3" t="s">
         <v>2592</v>
       </c>
@@ -22558,7 +22558,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="653" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A653" s="3" t="s">
         <v>2595</v>
       </c>
@@ -22578,7 +22578,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="654" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A654" s="3" t="s">
         <v>2598</v>
       </c>
@@ -22598,7 +22598,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="655" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A655" s="3" t="s">
         <v>2601</v>
       </c>
@@ -22618,7 +22618,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="656" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A656" s="3" t="s">
         <v>2605</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="657" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A657" s="3" t="s">
         <v>2608</v>
       </c>
@@ -22658,7 +22658,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="658" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A658" s="3" t="s">
         <v>2611</v>
       </c>
@@ -22678,7 +22678,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="659" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A659" s="3" t="s">
         <v>2614</v>
       </c>
@@ -22698,7 +22698,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="660" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A660" s="3" t="s">
         <v>2618</v>
       </c>
@@ -22718,7 +22718,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="661" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A661" s="3" t="s">
         <v>2622</v>
       </c>
@@ -22738,7 +22738,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="662" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A662" s="3" t="s">
         <v>2626</v>
       </c>
@@ -22758,7 +22758,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="663" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A663" s="3" t="s">
         <v>2630</v>
       </c>
@@ -22778,7 +22778,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="664" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A664" s="3" t="s">
         <v>2634</v>
       </c>
@@ -22798,7 +22798,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="665" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A665" s="3" t="s">
         <v>2639</v>
       </c>
@@ -22818,7 +22818,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="666" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A666" s="3" t="s">
         <v>2643</v>
       </c>
@@ -22838,7 +22838,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="667" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A667" s="3" t="s">
         <v>2647</v>
       </c>
@@ -22858,7 +22858,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="668" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A668" s="3" t="s">
         <v>2651</v>
       </c>
@@ -22878,7 +22878,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="669" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A669" s="3" t="s">
         <v>2655</v>
       </c>
@@ -22898,7 +22898,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="670" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A670" s="3" t="s">
         <v>2659</v>
       </c>
@@ -22918,7 +22918,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="671" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A671" s="3" t="s">
         <v>2663</v>
       </c>
@@ -22938,7 +22938,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="672" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A672" s="3" t="s">
         <v>2336</v>
       </c>
@@ -22958,7 +22958,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="673" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A673" s="3" t="s">
         <v>2669</v>
       </c>
@@ -22978,7 +22978,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="674" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A674" s="3" t="s">
         <v>2673</v>
       </c>
@@ -22998,7 +22998,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="675" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A675" s="3" t="s">
         <v>2678</v>
       </c>
@@ -23018,7 +23018,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="676" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A676" s="3" t="s">
         <v>2683</v>
       </c>
@@ -23038,7 +23038,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="677" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A677" s="3" t="s">
         <v>2688</v>
       </c>
@@ -23058,7 +23058,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="678" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A678" s="3" t="s">
         <v>2693</v>
       </c>
@@ -23078,7 +23078,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="679" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A679" s="3" t="s">
         <v>2696</v>
       </c>
@@ -23098,7 +23098,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="680" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A680" s="3" t="s">
         <v>2700</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="681" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A681" s="3" t="s">
         <v>2704</v>
       </c>
@@ -23138,7 +23138,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="682" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A682" s="3" t="s">
         <v>2709</v>
       </c>
@@ -23158,7 +23158,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="683" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A683" s="3" t="s">
         <v>2710</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="684" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A684" s="3" t="s">
         <v>2711</v>
       </c>
@@ -23198,7 +23198,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="685" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A685" s="3" t="s">
         <v>2712</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="686" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A686" s="3" t="s">
         <v>2713</v>
       </c>
@@ -23238,7 +23238,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="687" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A687" s="3" t="s">
         <v>2714</v>
       </c>
@@ -23258,7 +23258,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="688" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A688" s="3" t="s">
         <v>2715</v>
       </c>
@@ -23278,7 +23278,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="689" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A689" s="3" t="s">
         <v>2716</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="690" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A690" s="3" t="s">
         <v>2717</v>
       </c>
@@ -23318,7 +23318,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="691" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A691" s="3" t="s">
         <v>2718</v>
       </c>
@@ -23338,7 +23338,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="692" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A692" s="3" t="s">
         <v>2719</v>
       </c>
@@ -23358,7 +23358,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="693" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A693" s="3" t="s">
         <v>2720</v>
       </c>
@@ -23378,7 +23378,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="694" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A694" s="3" t="s">
         <v>2721</v>
       </c>
@@ -23398,7 +23398,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="695" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A695" s="3" t="s">
         <v>2722</v>
       </c>
@@ -23418,7 +23418,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="696" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A696" s="3" t="s">
         <v>2723</v>
       </c>
@@ -23438,7 +23438,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="697" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A697" s="3" t="s">
         <v>2724</v>
       </c>
@@ -23458,7 +23458,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="698" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A698" s="3" t="s">
         <v>2725</v>
       </c>
@@ -23478,7 +23478,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="699" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A699" s="3" t="s">
         <v>2726</v>
       </c>
@@ -23498,7 +23498,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="700" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A700" s="3" t="s">
         <v>2727</v>
       </c>
@@ -23518,7 +23518,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="701" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A701" s="3" t="s">
         <v>2728</v>
       </c>
@@ -23538,7 +23538,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="702" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A702" s="3" t="s">
         <v>2729</v>
       </c>
@@ -23558,7 +23558,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="703" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A703" s="3" t="s">
         <v>2730</v>
       </c>
@@ -23578,7 +23578,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="704" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A704" s="3" t="s">
         <v>2731</v>
       </c>
@@ -23598,7 +23598,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="705" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A705" s="3" t="s">
         <v>2732</v>
       </c>
@@ -23618,7 +23618,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="706" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A706" s="3" t="s">
         <v>2816</v>
       </c>
@@ -23638,7 +23638,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="707" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A707" s="3" t="s">
         <v>2817</v>
       </c>
@@ -23658,7 +23658,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="708" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A708" s="5" t="s">
         <v>2826</v>
       </c>
@@ -23678,7 +23678,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="709" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A709" s="5" t="s">
         <v>2827</v>
       </c>
@@ -23698,7 +23698,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="710" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A710" s="3" t="s">
         <v>2835</v>
       </c>
@@ -23718,7 +23718,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="711" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A711" s="3" t="s">
         <v>2836</v>
       </c>
@@ -23738,7 +23738,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="712" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A712" s="3" t="s">
         <v>2837</v>
       </c>
@@ -23758,7 +23758,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="713" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A713" s="3" t="s">
         <v>2838</v>
       </c>
@@ -23778,7 +23778,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="714" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A714" s="3" t="s">
         <v>2839</v>
       </c>
@@ -23798,7 +23798,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="715" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A715" s="3" t="s">
         <v>503</v>
       </c>
@@ -23818,7 +23818,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="716" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A716" s="3" t="s">
         <v>2856</v>
       </c>
@@ -23838,7 +23838,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="717" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A717" s="3" t="s">
         <v>504</v>
       </c>
@@ -23858,7 +23858,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="718" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A718" s="3" t="s">
         <v>2863</v>
       </c>
@@ -23878,7 +23878,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="719" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A719" s="3" t="s">
         <v>2868</v>
       </c>
@@ -23898,7 +23898,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="720" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A720" s="3" t="s">
         <v>2873</v>
       </c>
@@ -23918,7 +23918,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="721" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A721" s="3" t="s">
         <v>2877</v>
       </c>
@@ -23938,7 +23938,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="722" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A722" s="3" t="s">
         <v>2882</v>
       </c>
@@ -23958,7 +23958,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="723" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A723" s="3" t="s">
         <v>2886</v>
       </c>
@@ -23978,7 +23978,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="724" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A724" s="3" t="s">
         <v>2891</v>
       </c>
@@ -23998,7 +23998,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="725" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A725" s="3" t="s">
         <v>2895</v>
       </c>
@@ -24018,7 +24018,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="726" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A726" s="3" t="s">
         <v>2899</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="727" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A727" s="3" t="s">
         <v>2904</v>
       </c>
@@ -24058,7 +24058,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="728" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A728" s="3" t="s">
         <v>2909</v>
       </c>
@@ -24078,7 +24078,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="729" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A729" s="3" t="s">
         <v>2913</v>
       </c>
@@ -24098,7 +24098,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="730" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A730" s="3" t="s">
         <v>2918</v>
       </c>
@@ -24118,7 +24118,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="731" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A731" s="3" t="s">
         <v>2923</v>
       </c>
@@ -24138,7 +24138,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="732" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A732" s="3" t="s">
         <v>2927</v>
       </c>
@@ -24158,7 +24158,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="733" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A733" s="3" t="s">
         <v>2932</v>
       </c>
@@ -24178,7 +24178,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="734" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A734" s="3" t="s">
         <v>2936</v>
       </c>
@@ -24198,7 +24198,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="735" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A735" s="3" t="s">
         <v>2941</v>
       </c>
@@ -24218,7 +24218,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="736" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A736" s="3" t="s">
         <v>2946</v>
       </c>
@@ -24238,7 +24238,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="737" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A737" s="3" t="s">
         <v>2950</v>
       </c>
@@ -24258,7 +24258,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="738" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A738" s="3" t="s">
         <v>2955</v>
       </c>
@@ -24278,7 +24278,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="739" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A739" s="3" t="s">
         <v>2960</v>
       </c>
@@ -24298,7 +24298,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="740" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A740" s="3" t="s">
         <v>2965</v>
       </c>
@@ -24318,7 +24318,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="741" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A741" s="3" t="s">
         <v>2969</v>
       </c>
@@ -24338,7 +24338,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="742" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A742" s="3" t="s">
         <v>2974</v>
       </c>
@@ -24358,7 +24358,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="743" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A743" s="3" t="s">
         <v>2978</v>
       </c>
@@ -24378,7 +24378,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="744" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A744" s="3" t="s">
         <v>2982</v>
       </c>
@@ -24398,7 +24398,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="745" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A745" s="3" t="s">
         <v>2987</v>
       </c>
@@ -24418,7 +24418,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="746" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A746" s="3" t="s">
         <v>2991</v>
       </c>
